--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141451014823187</v>
+        <v>7.141447448051267</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.1515739224342</v>
+        <v>7.151567961264181</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155087351203756</v>
+        <v>7.155081485027623</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16844258682432</v>
+        <v>7.168436009090877</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183408286046174</v>
+        <v>7.183402051448536</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19536215939166</v>
+        <v>7.195356356403104</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197651975328624</v>
+        <v>7.197646728178631</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192198936300267</v>
+        <v>7.192194292909614</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175506218193879</v>
+        <v>7.175508893691914</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.1803760171276</v>
+        <v>7.180382582832722</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184411205815397</v>
+        <v>7.184417366610256</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189510779543191</v>
+        <v>7.189516866739679</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183326413471891</v>
+        <v>7.183337404096948</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182501112857166</v>
+        <v>7.182513939464271</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183563458932774</v>
+        <v>7.183574183526335</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168844546216115</v>
+        <v>7.168853895258948</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155477103829962</v>
+        <v>7.155490991984364</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148304799745043</v>
+        <v>7.148320667452748</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.14415735918313</v>
+        <v>7.144177139484723</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.12419505309837</v>
+        <v>7.124211248721114</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11163319425315</v>
+        <v>7.111655156570514</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.10307092274108</v>
+        <v>7.103095816949188</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075350706282556</v>
+        <v>7.075378629675391</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050755018123462</v>
+        <v>7.050783657776156</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049116736687098</v>
+        <v>7.049147098190716</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047679196723072</v>
+        <v>7.047716792532237</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054666301008563</v>
+        <v>7.054712481377577</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060316839925454</v>
+        <v>7.060380735935529</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015761756151985</v>
+        <v>7.015820125681794</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968197494496094</v>
+        <v>6.968245078683538</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968799507667458</v>
+        <v>6.96884605557025</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949036989973997</v>
+        <v>6.949096640662043</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898440346260188</v>
+        <v>6.898473111689015</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861910369568017</v>
+        <v>6.861944770711792</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847567343898588</v>
+        <v>6.847596364157296</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823830032190152</v>
+        <v>6.823806512611831</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842474481777926</v>
+        <v>6.84244391746511</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856597649279449</v>
+        <v>6.856532234914672</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887881820938985</v>
+        <v>6.887850151830069</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890299572253221</v>
+        <v>6.890277978744617</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877706422208937</v>
+        <v>6.877669119858396</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872113595471641</v>
+        <v>6.872138327370262</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846125189563772</v>
+        <v>6.846139655275675</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842142687122804</v>
+        <v>6.842166870936996</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807377423693177</v>
+        <v>6.807342491399394</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823965856152384</v>
+        <v>6.823967787960687</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818991642594668</v>
+        <v>6.819016699101336</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81366325566277</v>
+        <v>6.813691941870003</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807675732843469</v>
+        <v>6.807708915451627</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803302451402061</v>
+        <v>6.803338758200557</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801613942021162</v>
+        <v>6.801653179009061</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783652425114305</v>
+        <v>6.783666940376506</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784276331342271</v>
+        <v>6.78430216622924</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775583540613288</v>
+        <v>6.775594375139296</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772279542341751</v>
+        <v>6.772281459434954</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768299753963592</v>
+        <v>6.768303415805519</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762184466360259</v>
+        <v>6.762195566925649</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.75282055276003</v>
+        <v>6.752838230466844</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740668935283237</v>
+        <v>6.740693840728049</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728474166199662</v>
+        <v>6.728504416434235</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718657596537502</v>
+        <v>6.718338052669473</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.713297224522567</v>
+        <v>6.712941389403049</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.710481355985825</v>
+        <v>6.710149968658103</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.708619737858625</v>
+        <v>6.708073454104682</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.697553060383791</v>
+        <v>6.697047137794113</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683124508306807</v>
+        <v>6.682862372126646</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.666541845978964</v>
+        <v>6.666830789184484</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.641487582476044</v>
+        <v>6.642944745924542</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.639315987244158</v>
+        <v>6.641684605818702</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.645199727522768</v>
+        <v>6.648899596749549</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.671755012563433</v>
+        <v>6.676433215184288</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.680449378719679</v>
+        <v>6.687756368786471</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.709070180568981</v>
+        <v>6.719309779131369</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.732439890636634</v>
+        <v>6.751034086418435</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141447448051267</v>
+        <v>7.141443956360873</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151567961264181</v>
+        <v>7.151562125222334</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155081485027623</v>
+        <v>7.155075741200339</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168436009090877</v>
+        <v>7.168429568406716</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183402051448536</v>
+        <v>7.183395946835216</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195356356403104</v>
+        <v>7.195350674478716</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197646728178631</v>
+        <v>7.19764159050994</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192194292909614</v>
+        <v>7.192189746376195</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175508893691914</v>
+        <v>7.175511509771369</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180382582832722</v>
+        <v>7.180389009521523</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184417366610256</v>
+        <v>7.1844233970722</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189516866739679</v>
+        <v>7.189522825239704</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183337404096948</v>
+        <v>7.183348162490507</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182513939464271</v>
+        <v>7.182526496084983</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183574183526335</v>
+        <v>7.183584682379134</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168853895258948</v>
+        <v>7.16886304500102</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155490991984364</v>
+        <v>7.155504585377187</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148320667452748</v>
+        <v>7.148336198739775</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144177139484723</v>
+        <v>7.144196503089997</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124211248721114</v>
+        <v>7.124227100043085</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111655156570514</v>
+        <v>7.111676657958534</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103095816949188</v>
+        <v>7.103120192907621</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075378629675391</v>
+        <v>7.075405978828138</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050783657776156</v>
+        <v>7.050811708853132</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049147098190716</v>
+        <v>7.049176832525617</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047716792532237</v>
+        <v>7.047753603501581</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054712481377577</v>
+        <v>7.054757692983892</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060380735935529</v>
+        <v>7.060443286126034</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015820125681794</v>
+        <v>7.015877256114958</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968245078683538</v>
+        <v>6.968291664972993</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.96884605557025</v>
+        <v>6.968891638535392</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949096640662043</v>
+        <v>6.949155097769719</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898473111689015</v>
+        <v>6.898505231358361</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861944770711792</v>
+        <v>6.861978498470217</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847596364157296</v>
+        <v>6.847624839566461</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823806512611831</v>
+        <v>6.823783509581844</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.84244391746511</v>
+        <v>6.842414014625985</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856532234914672</v>
+        <v>6.856468167886696</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887850151830069</v>
+        <v>6.887819133481047</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890277978744617</v>
+        <v>6.890256809530605</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877669119858396</v>
+        <v>6.87763255180988</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872138327370262</v>
+        <v>6.872162552059907</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846139655275675</v>
+        <v>6.846153835196175</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842166870936996</v>
+        <v>6.842190575068073</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807342491399394</v>
+        <v>6.807308238512382</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823967787960687</v>
+        <v>6.823969655596676</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819016699101336</v>
+        <v>6.819041212460803</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813691941870003</v>
+        <v>6.813720008372737</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807708915451627</v>
+        <v>6.807741392412725</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803338758200557</v>
+        <v>6.803374308054835</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801653179009061</v>
+        <v>6.801691621017537</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783666940376506</v>
+        <v>6.783681152656093</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.78430216622924</v>
+        <v>6.78432749011606</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775594375139296</v>
+        <v>6.775605015764455</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772281459434954</v>
+        <v>6.772283362284445</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768303415805519</v>
+        <v>6.768306996823695</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762195566925649</v>
+        <v>6.762206394874884</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752838230466844</v>
+        <v>6.752855496565999</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740693840728049</v>
+        <v>6.740718189250883</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728504416434235</v>
+        <v>6.728534077537566</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718338052669473</v>
+        <v>6.718366878831907</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712941389403049</v>
+        <v>6.712845800451355</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.710149968658103</v>
+        <v>6.710045019555819</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.708073454104682</v>
+        <v>6.707885259021785</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.697047137794113</v>
+        <v>6.696832342477722</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.682862372126646</v>
+        <v>6.682835726038677</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.666830789184484</v>
+        <v>6.667128954567389</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.642944745924542</v>
+        <v>6.643968054940162</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.641684605818702</v>
+        <v>6.64291080373333</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.648899596749549</v>
+        <v>6.650116125007496</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.676433215184288</v>
+        <v>6.676888838322707</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.687756368786471</v>
+        <v>6.688071059570579</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.719309779131369</v>
+        <v>6.717632670195227</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,15 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.751034086418435</v>
+        <v>6.744457168935337</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>6.709197793935338</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141443956360873</v>
+        <v>7.141440537406052</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151562125222334</v>
+        <v>7.151556410410134</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155075741200339</v>
+        <v>7.155070115934471</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168429568406716</v>
+        <v>7.168423260533767</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183395946835216</v>
+        <v>7.183389968183966</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195350674478716</v>
+        <v>7.195345109869805</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.19764159050994</v>
+        <v>7.197636558932063</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192189746376195</v>
+        <v>7.192185293701257</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175511509771369</v>
+        <v>7.17551406838415</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180389009521523</v>
+        <v>7.180395301562084</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.1844233970722</v>
+        <v>7.184429301293092</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189522825239704</v>
+        <v>7.189528659081313</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183348162490507</v>
+        <v>7.183358695934223</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182526496084983</v>
+        <v>7.182538791151568</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183584682379134</v>
+        <v>7.183594962542664</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.16886304500102</v>
+        <v>7.16887200174469</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155504585377187</v>
+        <v>7.155517893288091</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148336198739775</v>
+        <v>7.14835140418392</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144196503089997</v>
+        <v>7.14421546302227</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124227100043085</v>
+        <v>7.124242617920578</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111676657958534</v>
+        <v>7.111697712763403</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103120192907621</v>
+        <v>7.103144066613683</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075405978828138</v>
+        <v>7.075432771252981</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050811708853132</v>
+        <v>7.050839189290011</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049176832525617</v>
+        <v>7.049205958903833</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047753603501581</v>
+        <v>7.047789653929502</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054757692983892</v>
+        <v>7.054801965958714</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060443286126034</v>
+        <v>7.060504532509198</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015877256114958</v>
+        <v>7.015933186439572</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968291664972993</v>
+        <v>6.968337284348674</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968891638535392</v>
+        <v>6.968936286170202</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949155097769719</v>
+        <v>6.949212396643768</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898505231358361</v>
+        <v>6.898536724077944</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861978498470217</v>
+        <v>6.862011572309482</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847624839566461</v>
+        <v>6.84765278511066</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823783509581844</v>
+        <v>6.823761006341963</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842414014625985</v>
+        <v>6.842384752092444</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856468167886696</v>
+        <v>6.856405407064377</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887819133481047</v>
+        <v>6.887788746075752</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890256809530605</v>
+        <v>6.890236052314338</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87763255180988</v>
+        <v>6.87759669669871</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872162552059907</v>
+        <v>6.872186284977487</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846153835196175</v>
+        <v>6.846167737692406</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842190575068073</v>
+        <v>6.842213813630499</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807308238512382</v>
+        <v>6.807274645538633</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823969655596676</v>
+        <v>6.823971461768462</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819041212460803</v>
+        <v>6.819065200083164</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813720008372737</v>
+        <v>6.813747474962437</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807741392412725</v>
+        <v>6.80777318593128</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803374308054835</v>
+        <v>6.803409124328883</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801691621017537</v>
+        <v>6.801729291883211</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783681152656093</v>
+        <v>6.783695071296281</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.78432749011606</v>
+        <v>6.784352317922471</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775605015764455</v>
+        <v>6.775615467509626</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772283362284445</v>
+        <v>6.772285250602732</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768306996823695</v>
+        <v>6.768310499725366</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762206394874884</v>
+        <v>6.762216959841203</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752855496565999</v>
+        <v>6.752872364803789</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740718189250883</v>
+        <v>6.740741998692625</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728534077537566</v>
+        <v>6.728563165841464</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718366878831907</v>
+        <v>6.718395227621373</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712845800451355</v>
+        <v>6.71261145391278</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.710045019555819</v>
+        <v>6.7097625926007</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707885259021785</v>
+        <v>6.707497074549915</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696832342477722</v>
+        <v>6.696383668635295</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.682835726038677</v>
+        <v>6.682540082016605</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.667128954567389</v>
+        <v>6.667109624347102</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.643968054940162</v>
+        <v>6.64457899842874</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.64291080373333</v>
+        <v>6.643636746328506</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.650116125007496</v>
+        <v>6.650756055547397</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.676888838322707</v>
+        <v>6.676655658236649</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.688071059570579</v>
+        <v>6.68751834051588</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.717632670195227</v>
+        <v>6.715030676334569</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.744457168935337</v>
+        <v>6.737471509894261</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.709197793935338</v>
+        <v>6.702212134894262</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141440537406052</v>
+        <v>7.141437188937574</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151556410410134</v>
+        <v>7.151550813089324</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155070115934471</v>
+        <v>7.155064605597293</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168423260533767</v>
+        <v>7.168417081406885</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183389968183966</v>
+        <v>7.183384111636762</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195345109869805</v>
+        <v>7.195339658980835</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197636558932063</v>
+        <v>7.197631630193057</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192185293701257</v>
+        <v>7.192180932008545</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.17551406838415</v>
+        <v>7.175516571397821</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180395301562084</v>
+        <v>7.180401463141425</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184429301293092</v>
+        <v>7.184435083195315</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189528659081313</v>
+        <v>7.189534372135401</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183358695934223</v>
+        <v>7.183369011408553</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182538791151568</v>
+        <v>7.1825508327489</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183594962542664</v>
+        <v>7.183605030777811</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.16887200174469</v>
+        <v>7.168880771529491</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155517893288091</v>
+        <v>7.155530924611496</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14835140418392</v>
+        <v>7.14836629392449</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.14421546302227</v>
+        <v>7.144234031768029</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124242617920578</v>
+        <v>7.124257812758504</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111697712763403</v>
+        <v>7.111718334742616</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103144066613683</v>
+        <v>7.103167453413777</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075432771252981</v>
+        <v>7.075459023758063</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050839189290011</v>
+        <v>7.050866116301975</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049205958903833</v>
+        <v>7.049234495761532</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047789653929502</v>
+        <v>7.047824967122572</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054801965958714</v>
+        <v>7.054845329197981</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060504532509198</v>
+        <v>7.060564515369208</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015933186439572</v>
+        <v>7.015987954027191</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968337284348674</v>
+        <v>6.968381966528479</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968936286170202</v>
+        <v>6.968980026886674</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949212396643768</v>
+        <v>6.949268571254001</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898536724077944</v>
+        <v>6.898567607937957</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862011572309482</v>
+        <v>6.862044010957447</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84765278511066</v>
+        <v>6.847680215239575</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823761006341963</v>
+        <v>6.823738986848298</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842384752092444</v>
+        <v>6.842356109587143</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856405407064377</v>
+        <v>6.856343912971019</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887788746075752</v>
+        <v>6.887758970592921</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890236052314338</v>
+        <v>6.890215695265852</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87759669669871</v>
+        <v>6.877561533976554</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872186284977487</v>
+        <v>6.872209540940073</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846167737692406</v>
+        <v>6.846181370808797</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842213813630499</v>
+        <v>6.842236600190996</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807274645538633</v>
+        <v>6.807241693717508</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823971461768462</v>
+        <v>6.82397320904483</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819065200083164</v>
+        <v>6.819088678644679</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813747474962437</v>
+        <v>6.813774360599612</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.80777318593128</v>
+        <v>6.807804317292566</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803409124328883</v>
+        <v>6.803443229437518</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801729291883211</v>
+        <v>6.801766214502571</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783695071296281</v>
+        <v>6.783708705261871</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784352317922471</v>
+        <v>6.784376663996929</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775615467509626</v>
+        <v>6.775625735230028</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772285250602732</v>
+        <v>6.772287124140927</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768310499725366</v>
+        <v>6.768313927096347</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762216959841203</v>
+        <v>6.762227271019539</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752872364803789</v>
+        <v>6.752888848337554</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740741998692625</v>
+        <v>6.740765286162752</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728563165841464</v>
+        <v>6.728591697109042</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718395227621373</v>
+        <v>6.718423109772081</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.71261145391278</v>
+        <v>6.712538878005336</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.7097625926007</v>
+        <v>6.709682378800088</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707497074549915</v>
+        <v>6.70734214738494</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696383668635295</v>
+        <v>6.696169632215302</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.682540082016605</v>
+        <v>6.682476973592911</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.667109624347102</v>
+        <v>6.667332736463328</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.64457899842874</v>
+        <v>6.645466889789758</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.643636746328506</v>
+        <v>6.644739458585008</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.650756055547397</v>
+        <v>6.651922473301426</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.676655658236649</v>
+        <v>6.677320717590796</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.68751834051588</v>
+        <v>6.688303379420065</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.715030676334569</v>
+        <v>6.714718515987782</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.737471509894261</v>
+        <v>6.735250571475503</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.702212134894262</v>
+        <v>6.703734310888214</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141437188937574</v>
+        <v>7.141433908798</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151550813089324</v>
+        <v>7.151545329673772</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155064605597293</v>
+        <v>7.15505920670295</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168417081406885</v>
+        <v>7.168411027125114</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183384111636762</v>
+        <v>7.183378373491514</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195339658980835</v>
+        <v>7.195334318361692</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197631630193057</v>
+        <v>7.19762680117252</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192180932008545</v>
+        <v>7.192176658538128</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175516571397821</v>
+        <v>7.175519020600087</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180401463141425</v>
+        <v>7.180407498274763</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184435083195315</v>
+        <v>7.184440746540445</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189534372135401</v>
+        <v>7.189539968114254</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183369011408553</v>
+        <v>7.183379115608165</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.1825508327489</v>
+        <v>7.18256262863216</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183605030777811</v>
+        <v>7.183614893569684</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168880771529491</v>
+        <v>7.168889360145695</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155530924611496</v>
+        <v>7.155543687876348</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14836629392449</v>
+        <v>7.148380877684767</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144234031768029</v>
+        <v>7.144252221304288</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124257812758504</v>
+        <v>7.124272694533607</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111718334742616</v>
+        <v>7.111738537094835</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103167453413777</v>
+        <v>7.103190368036118</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075459023758063</v>
+        <v>7.075484752482476</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050866116301975</v>
+        <v>7.050892506419535</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049234495761532</v>
+        <v>7.049262460797745</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047824967122572</v>
+        <v>7.047859565445597</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054845329197981</v>
+        <v>7.054887810424948</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060564515369208</v>
+        <v>7.060623273350028</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015987954027191</v>
+        <v>7.016041594715658</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968381966528479</v>
+        <v>6.968425740027851</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968980026886674</v>
+        <v>6.969022887961017</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949268571254001</v>
+        <v>6.949323654259423</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898567607937957</v>
+        <v>6.898597900342946</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862044010957447</v>
+        <v>6.86207583243806</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847680215239575</v>
+        <v>6.847707143891126</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823738986848298</v>
+        <v>6.82371743573378</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842356109587143</v>
+        <v>6.842328067677283</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856343912971019</v>
+        <v>6.856283647702137</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887758970592921</v>
+        <v>6.887729788766809</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890215695265852</v>
+        <v>6.890195727000314</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877561533976554</v>
+        <v>6.877527043873031</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872209540940073</v>
+        <v>6.872232334175663</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846181370808797</v>
+        <v>6.846194742282437</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842236600190996</v>
+        <v>6.842258947794829</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807241693717508</v>
+        <v>6.807209364987436</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82397320904483</v>
+        <v>6.823974899863689</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819088678644679</v>
+        <v>6.819111664125911</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813774360599612</v>
+        <v>6.813800683456819</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807804317292566</v>
+        <v>6.807834806909549</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803443229437518</v>
+        <v>6.803476644893965</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801766214502571</v>
+        <v>6.801802410877698</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783708705261871</v>
+        <v>6.783722063158118</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784376663996929</v>
+        <v>6.784400542143478</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775625735230028</v>
+        <v>6.775635823621659</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772287124140927</v>
+        <v>6.772288982685596</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768313927096347</v>
+        <v>6.768317281407805</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762227271019539</v>
+        <v>6.7622373371907</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752888848337554</v>
+        <v>6.752904959766166</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740765286162752</v>
+        <v>6.740788068075394</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728591697109042</v>
+        <v>6.728619686557692</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718423109772081</v>
+        <v>6.71845053574572</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712538878005336</v>
+        <v>6.712460107436576</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709682378800088</v>
+        <v>6.709590796703573</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.70734214738494</v>
+        <v>6.707174161242572</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696169632215302</v>
+        <v>6.695909235216742</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.682476973592911</v>
+        <v>6.682320743349138</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.667332736463328</v>
+        <v>6.667425186047473</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.645466889789758</v>
+        <v>6.646172481217379</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.644739458585008</v>
+        <v>6.645638485376621</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.651922473301426</v>
+        <v>6.652893787491244</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.677320717590796</v>
+        <v>6.677834152479739</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.688303379420065</v>
+        <v>6.68898474792978</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.714718515987782</v>
+        <v>6.714530728772492</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.735250571475503</v>
+        <v>6.733766874709692</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.703734310888214</v>
+        <v>6.709559921032334</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141433908798</v>
+        <v>7.14143069491704</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151545329673772</v>
+        <v>7.151539956721811</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15505920670295</v>
+        <v>7.155053915905127</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168411027125114</v>
+        <v>7.168405093943488</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183378373491514</v>
+        <v>7.18337275019426</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195334318361692</v>
+        <v>7.195329084700397</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.19762680117252</v>
+        <v>7.197622068875004</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192176658538128</v>
+        <v>7.192172470640564</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175519020600087</v>
+        <v>7.175521417703015</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180407498274763</v>
+        <v>7.180413410814259</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184440746540445</v>
+        <v>7.184446294937414</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189539968114254</v>
+        <v>7.18954545057961</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183379115608165</v>
+        <v>7.183389014956419</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.18256262863216</v>
+        <v>7.182574186243469</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183614893569684</v>
+        <v>7.183624557141527</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168889360145695</v>
+        <v>7.168897773147028</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155543687876348</v>
+        <v>7.155556191264702</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148380877684767</v>
+        <v>7.148395164793117</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144252221304288</v>
+        <v>7.144270043124308</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124272694533607</v>
+        <v>7.124287272816246</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111738537094835</v>
+        <v>7.111758332487955</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103190368036118</v>
+        <v>7.103212824621528</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075484752482476</v>
+        <v>7.075509972929172</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050892506419535</v>
+        <v>7.050918375522169</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049262460797745</v>
+        <v>7.049289871010805</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047859565445597</v>
+        <v>7.047893470368652</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054887810424948</v>
+        <v>7.054929436249013</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060623273350028</v>
+        <v>7.060680843537909</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016041594715658</v>
+        <v>7.016094142886868</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968425740027851</v>
+        <v>6.968468632219849</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969022887961017</v>
+        <v>6.969064895589668</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949323654259423</v>
+        <v>6.949377677070627</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898597900342946</v>
+        <v>6.898627618043795</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.86207583243806</v>
+        <v>6.862107054103889</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847707143891126</v>
+        <v>6.847733584513437</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82371743573378</v>
+        <v>6.823696338272952</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842328067677283</v>
+        <v>6.842300607731209</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856283647702137</v>
+        <v>6.856224574848115</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887729788766809</v>
+        <v>6.887701183050136</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890195727000314</v>
+        <v>6.890176136557473</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877527043873031</v>
+        <v>6.877493207359473</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872232334175663</v>
+        <v>6.872254678352174</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846194742282437</v>
+        <v>6.84620785955758</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842258947794829</v>
+        <v>6.84228086899059</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807209364987436</v>
+        <v>6.807177641953919</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823974899863689</v>
+        <v>6.82397653653994</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819111664125911</v>
+        <v>6.819134171847526</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813800683456819</v>
+        <v>6.813826460959047</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807834806909549</v>
+        <v>6.807864674366995</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803476644893965</v>
+        <v>6.803509391354623</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801802410877698</v>
+        <v>6.801837902159356</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783722063158118</v>
+        <v>6.783735153248495</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784400542143478</v>
+        <v>6.784423965647145</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775635823621659</v>
+        <v>6.775645737227446</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772288982685596</v>
+        <v>6.772290826055841</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768317281407805</v>
+        <v>6.768320565022606</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.7622373371907</v>
+        <v>6.762247166743995</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752904959766166</v>
+        <v>6.752920711158643</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740788068075394</v>
+        <v>6.740810360183344</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728619686557692</v>
+        <v>6.728647148881034</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.71845053574572</v>
+        <v>6.71847751573715</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712460107436576</v>
+        <v>6.712384357822512</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709590796703573</v>
+        <v>6.709534401096565</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707174161242572</v>
+        <v>6.707107538162328</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.695909235216742</v>
+        <v>6.695945401632903</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.682320743349138</v>
+        <v>6.682628142912431</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.667425186047473</v>
+        <v>6.668096936841424</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.646172481217379</v>
+        <v>6.647497271633204</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.645638485376621</v>
+        <v>6.647143100185107</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.652893787491244</v>
+        <v>6.654361312605429</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.677834152479739</v>
+        <v>6.678758686694556</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.68898474792978</v>
+        <v>6.6896618396422</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.714530728772492</v>
+        <v>6.713743137333232</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.733766874709692</v>
+        <v>6.730723385798324</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.709559921032334</v>
+        <v>6.707316366454104</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.14143069491704</v>
+        <v>7.141427545307208</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151539956721811</v>
+        <v>7.151534690929029</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155053915905127</v>
+        <v>7.155048729990132</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168405093943488</v>
+        <v>7.168399278265305</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.18337275019426</v>
+        <v>7.183367238331837</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195329084700397</v>
+        <v>7.19532395481627</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197622068875004</v>
+        <v>7.197617430423826</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192172470640564</v>
+        <v>7.192168365771428</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175521417703015</v>
+        <v>7.175523764346995</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180413410814259</v>
+        <v>7.18041920445719</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184446294937414</v>
+        <v>7.184451731850167</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18954545057961</v>
+        <v>7.18955082295019</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183389014956419</v>
+        <v>7.183398715618967</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182574186243469</v>
+        <v>7.182585512727523</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183624557141527</v>
+        <v>7.183634027467794</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168897773147028</v>
+        <v>7.168906015862624</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155556191264702</v>
+        <v>7.155568442629154</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148395164793117</v>
+        <v>7.148409164202818</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144270043124308</v>
+        <v>7.144287508261752</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124287272816246</v>
+        <v>7.124301556790859</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111758332487955</v>
+        <v>7.111777733085493</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103212824621528</v>
+        <v>7.103234836752387</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075509972929172</v>
+        <v>7.075534699995966</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050918375522169</v>
+        <v>7.050943738870048</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049289871010805</v>
+        <v>7.049316742732643</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047893470368652</v>
+        <v>7.047926702511354</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054929436249013</v>
+        <v>7.054970232221033</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060680843537909</v>
+        <v>7.060737261538987</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016094142886868</v>
+        <v>7.016145631539873</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968468632219849</v>
+        <v>6.968510669391638</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969064895589668</v>
+        <v>6.96910607494204</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949377677070627</v>
+        <v>6.94943066990865</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898627618043795</v>
+        <v>6.898656777167951</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862107054103889</v>
+        <v>6.862137692666884</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847733584513437</v>
+        <v>6.847759550085708</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823696338272952</v>
+        <v>6.823675680348952</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842300607731209</v>
+        <v>6.842273711877683</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856224574848115</v>
+        <v>6.856166659421348</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887701183050136</v>
+        <v>6.88767313657916</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890176136557473</v>
+        <v>6.890156913382212</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877493207359473</v>
+        <v>6.877460006114664</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872254678352174</v>
+        <v>6.872276586604713</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84620785955758</v>
+        <v>6.846220729799349</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.84228086899059</v>
+        <v>6.842302375853597</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807177641953919</v>
+        <v>6.807146507859298</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82397653653994</v>
+        <v>6.823978121272788</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819134171847526</v>
+        <v>6.819156216503912</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813826460959047</v>
+        <v>6.81385170982164</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807864674366995</v>
+        <v>6.807893938462952</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803509391354623</v>
+        <v>6.803541488661192</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801837902159356</v>
+        <v>6.801872708687622</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783735153248495</v>
+        <v>6.783747983471418</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784423965647145</v>
+        <v>6.784446947297917</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775645737227446</v>
+        <v>6.775655480443131</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772290826055841</v>
+        <v>6.772292654100642</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768320565022606</v>
+        <v>6.76832378020124</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762247166743995</v>
+        <v>6.762256767698412</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752920711158643</v>
+        <v>6.75293611408107</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740810360183344</v>
+        <v>6.740832177610146</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728647148881034</v>
+        <v>6.728674098269931</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.71847751573715</v>
+        <v>6.71850405968021</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712384357822512</v>
+        <v>6.712281123209077</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709534401096565</v>
+        <v>6.709450206365855</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707107538162328</v>
+        <v>6.707013615388274</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.695945401632903</v>
+        <v>6.695919164854306</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.682628142912431</v>
+        <v>6.682845517993638</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.668096936841424</v>
+        <v>6.668649352691501</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.647497271633204</v>
+        <v>6.648655556566755</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.647143100185107</v>
+        <v>6.648452941423566</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.654361312605429</v>
+        <v>6.655621943858485</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.678758686694556</v>
+        <v>6.679473313430053</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.6896618396422</v>
+        <v>6.690113098095134</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.713743137333232</v>
+        <v>6.712829759554841</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.730723385798324</v>
+        <v>6.727858873470502</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.707316366454104</v>
+        <v>6.705216121986114</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141427545307208</v>
+        <v>7.14142445805971</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151534690929029</v>
+        <v>7.151529529121508</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155048729990132</v>
+        <v>7.155043645870383</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168399278265305</v>
+        <v>7.168393576634866</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183367238331837</v>
+        <v>7.183361834624973</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19532395481627</v>
+        <v>7.195318925653485</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197617430423826</v>
+        <v>7.197612883055239</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192168365771428</v>
+        <v>7.192164341486171</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175523764346995</v>
+        <v>7.175526062104421</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.18041920445719</v>
+        <v>7.180424882753663</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184451731850167</v>
+        <v>7.184457060604876</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18955082295019</v>
+        <v>7.189556088508822</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183398715618967</v>
+        <v>7.183408223516541</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182585512727523</v>
+        <v>7.182596614946294</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183634027467794</v>
+        <v>7.183643310286467</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168906015862624</v>
+        <v>7.168914093408251</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155568442629154</v>
+        <v>7.155580449509267</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148409164202818</v>
+        <v>7.148422884510721</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144287508261752</v>
+        <v>7.144304627313434</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124301556790859</v>
+        <v>7.124315555275221</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111777733085493</v>
+        <v>7.111796750571427</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103234836752387</v>
+        <v>7.103256417479908</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075534699995966</v>
+        <v>7.075558948004748</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050943738870048</v>
+        <v>7.050968611133869</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049316742732643</v>
+        <v>7.049343091661088</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047926702511354</v>
+        <v>7.047959281684514</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054970232221033</v>
+        <v>7.055010222885391</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060737261538987</v>
+        <v>7.060792561552293</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016145631539873</v>
+        <v>7.016196092359635</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968510669391638</v>
+        <v>6.968551876797688</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.96910607494204</v>
+        <v>6.969146450210228</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.94943066990865</v>
+        <v>6.949482661860547</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898656777167951</v>
+        <v>6.898685393248</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862137692666884</v>
+        <v>6.862167764227462</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847759550085708</v>
+        <v>6.847785053138078</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823675680348952</v>
+        <v>6.823655448422494</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842273711877683</v>
+        <v>6.842247362967568</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856166659421348</v>
+        <v>6.856109867787597</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.88767313657916</v>
+        <v>6.887645633140773</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890156913382212</v>
+        <v>6.890138047306165</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877460006114664</v>
+        <v>6.877427422492433</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872276586604713</v>
+        <v>6.872298071561276</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846220729799349</v>
+        <v>6.846233359906651</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842302375853597</v>
+        <v>6.842323480007968</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807146507859298</v>
+        <v>6.807115946554092</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823978121272788</v>
+        <v>6.823979656152561</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819156216503912</v>
+        <v>6.819177812194763</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81385170982164</v>
+        <v>6.813876446085961</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807893938462952</v>
+        <v>6.807922617247748</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803541488661192</v>
+        <v>6.803572955880343</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801872708687622</v>
+        <v>6.801906850030223</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783747983471418</v>
+        <v>6.783760561455998</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784446947297917</v>
+        <v>6.784469499413444</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775655480443131</v>
+        <v>6.775665057522908</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772292654100642</v>
+        <v>6.772294466696382</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76832378020124</v>
+        <v>6.768326929107363</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762256767698412</v>
+        <v>6.762266147722456</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.75293611408107</v>
+        <v>6.752951179621943</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740832177610146</v>
+        <v>6.740853534880372</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728674098269931</v>
+        <v>6.72870054843257</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.71850405968021</v>
+        <v>6.718530177253593</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712281123209077</v>
+        <v>6.712306242577196</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709450206365855</v>
+        <v>6.709578023975583</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707013615388274</v>
+        <v>6.707160359566648</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.695919164854306</v>
+        <v>6.696331632710068</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.682845517993638</v>
+        <v>6.683314117149421</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.668649352691501</v>
+        <v>6.669369939473413</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.648655556566755</v>
+        <v>6.649892691517923</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.648452941423566</v>
+        <v>6.649781655722486</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.655621943858485</v>
+        <v>6.656884962143843</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.679473313430053</v>
+        <v>6.680138650161298</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.690113098095134</v>
+        <v>6.690419373342101</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.712829759554841</v>
+        <v>6.711934126364834</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.727858873470502</v>
+        <v>6.725403088250914</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,15 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.705216121986114</v>
+        <v>6.703968293156995</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>6.697894392436021</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.14142445805971</v>
+        <v>7.141421431340601</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151529529121508</v>
+        <v>7.151524468249438</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155043645870383</v>
+        <v>7.155038660578297</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168393576634866</v>
+        <v>7.168387985730645</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183361834624973</v>
+        <v>7.183356535921797</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195318925653485</v>
+        <v>7.195313994275005</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197612883055239</v>
+        <v>7.197608424112948</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192164341486171</v>
+        <v>7.192160395435263</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175526062104421</v>
+        <v>7.175528312483189</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180424882753663</v>
+        <v>7.180430449113867</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184457060604876</v>
+        <v>7.184462284396715</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189556088508822</v>
+        <v>7.18956125040912</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183408223516541</v>
+        <v>7.183417544337001</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182596614946294</v>
+        <v>7.182607499492883</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183643310286467</v>
+        <v>7.183652411110633</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168914093408251</v>
+        <v>7.168922010696892</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155580449509267</v>
+        <v>7.155592219146988</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148422884510721</v>
+        <v>7.148436333974783</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144304627313434</v>
+        <v>7.144321410460703</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124315555275221</v>
+        <v>7.124329276738543</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111796750571427</v>
+        <v>7.111815396173566</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103256417479908</v>
+        <v>7.103277579349816</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075558948004748</v>
+        <v>7.075582730729009</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050968611133869</v>
+        <v>7.050993006423033</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049343091661088</v>
+        <v>7.049368932890321</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047959281684514</v>
+        <v>7.047991226929369</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055010222885391</v>
+        <v>7.055049431829017</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060792561552293</v>
+        <v>7.060846776438485</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016196092359635</v>
+        <v>7.016245555781712</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968551876797688</v>
+        <v>6.968592278709869</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969146450210228</v>
+        <v>6.969186044655844</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949482661860547</v>
+        <v>6.94953368093191</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898685393248</v>
+        <v>6.898713481248693</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862167764227462</v>
+        <v>6.862197284302068</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847785053138078</v>
+        <v>6.847810105770495</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823655448422494</v>
+        <v>6.82363562950273</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842247362967568</v>
+        <v>6.842221544537848</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856109867787597</v>
+        <v>6.856054167601304</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887645633140773</v>
+        <v>6.887618657141497</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890138047306165</v>
+        <v>6.890119528530298</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877427422492433</v>
+        <v>6.877395439491047</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872298071561276</v>
+        <v>6.872319145366983</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846233359906651</v>
+        <v>6.846245756524416</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842323480007968</v>
+        <v>6.842344192647484</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807115946554092</v>
+        <v>6.80708594246988</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823979656152561</v>
+        <v>6.823981143167064</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819177812194763</v>
+        <v>6.81919897245478</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813876446085961</v>
+        <v>6.813900685152902</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807922617247748</v>
+        <v>6.807950728060701</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803572955880343</v>
+        <v>6.8036038113411</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801906850030223</v>
+        <v>6.801940345018719</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783760561455998</v>
+        <v>6.783772894536892</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784469499413444</v>
+        <v>6.784491633860478</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775665057522908</v>
+        <v>6.775674472584828</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772294466696382</v>
+        <v>6.772296263744577</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768326929107363</v>
+        <v>6.768330013812967</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762266147722456</v>
+        <v>6.762275314152753</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752951179621943</v>
+        <v>6.752965918416016</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740853534880372</v>
+        <v>6.740874445948231</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.72870054843257</v>
+        <v>6.728726512613685</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718530177253593</v>
+        <v>6.718555877886774</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712306242577196</v>
+        <v>6.712331001772581</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709578023975583</v>
+        <v>6.709563370537865</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707160359566648</v>
+        <v>6.707129175002916</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696331632710068</v>
+        <v>6.696589748120047</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683314117149421</v>
+        <v>6.683510916743444</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.669369939473413</v>
+        <v>6.669757589613486</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.649892691517923</v>
+        <v>6.650715358400171</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.649781655722486</v>
+        <v>6.650627031980642</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.656884962143843</v>
+        <v>6.657618345559893</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.680138650161298</v>
+        <v>6.680234517537716</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.690419373342101</v>
+        <v>6.690024505048271</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.711934126364834</v>
+        <v>6.710272042597071</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.725403088250914</v>
+        <v>6.722110928369302</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.703968293156995</v>
+        <v>6.700936386213117</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.697894392436021</v>
+        <v>6.689946046972677</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709563370537865</v>
+        <v>6.709506099246068</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707129175002916</v>
+        <v>6.707060437007591</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696589748120047</v>
+        <v>6.696509957846345</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683510916743444</v>
+        <v>6.6834551245362</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.669757589613486</v>
+        <v>6.669710206756168</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.650715358400171</v>
+        <v>6.65066519801882</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.650627031980642</v>
+        <v>6.650568961371841</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.657618345559893</v>
+        <v>6.657545665713752</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.680234517537716</v>
+        <v>6.680137252005744</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.690024505048271</v>
+        <v>6.689904513696563</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.710272042597071</v>
+        <v>6.710113810527917</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.722110928369302</v>
+        <v>6.721891889135714</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.700936386213117</v>
+        <v>6.70053459524326</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.689946046972677</v>
+        <v>6.688319322590679</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141421431340601</v>
+        <v>7.141418463387144</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151524468249438</v>
+        <v>7.151519505381103</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155038660578297</v>
+        <v>7.155033771260507</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168387985730645</v>
+        <v>7.16838250235882</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183356535921797</v>
+        <v>7.183351339191703</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195313994275005</v>
+        <v>7.195309157856868</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197608424112948</v>
+        <v>7.197604051042938</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192160395435263</v>
+        <v>7.192156525359611</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175528312483189</v>
+        <v>7.175530516929959</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180430449113867</v>
+        <v>7.180435906814895</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184462284396715</v>
+        <v>7.184467406296251</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18956125040912</v>
+        <v>7.189566311681774</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183417544337001</v>
+        <v>7.18342668354666</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182607499492883</v>
+        <v>7.182618172704537</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183652411110633</v>
+        <v>7.183661335239387</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168922010696892</v>
+        <v>7.168929772448678</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155592219146988</v>
+        <v>7.155603758501197</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148436333974783</v>
+        <v>7.148449520530606</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144321410460703</v>
+        <v>7.144337867489604</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124329276738543</v>
+        <v>7.124342729318518</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111815396173566</v>
+        <v>7.111833680685598</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103277579349816</v>
+        <v>7.103298334426558</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075582730729009</v>
+        <v>7.075606061419811</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050993006423033</v>
+        <v>7.051016938312188</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049368932890321</v>
+        <v>7.049394280939584</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047991226929369</v>
+        <v>7.048022556554573</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055049431829017</v>
+        <v>7.055087881727576</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060846776438485</v>
+        <v>7.0608999377846</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016245555781712</v>
+        <v>7.016294051053166</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968592278709869</v>
+        <v>6.968631898464677</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969186044655844</v>
+        <v>6.969224880654211</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.94953368093191</v>
+        <v>6.949583754096478</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898713481248693</v>
+        <v>6.898741055592524</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862197284302068</v>
+        <v>6.862226267849222</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847810105770495</v>
+        <v>6.84783471967067</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82363562950273</v>
+        <v>6.823616211119842</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842221544537848</v>
+        <v>6.842196240777735</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856054167601304</v>
+        <v>6.855999527744522</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887618657141497</v>
+        <v>6.887592193578199</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890119528530298</v>
+        <v>6.890101347608432</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877395439491047</v>
+        <v>6.87736404072419</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872319145366983</v>
+        <v>6.872339819706929</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846245756524416</v>
+        <v>6.846257926055148</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842344192647484</v>
+        <v>6.842364524555299</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.80708594246988</v>
+        <v>6.807056480593618</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823981143167064</v>
+        <v>6.823982584207513</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.81919897245478</v>
+        <v>6.819219710281613</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813900685152902</v>
+        <v>6.813924441814453</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807950728060701</v>
+        <v>6.807978287564715</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.8036038113411</v>
+        <v>6.803634072670082</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801940345018719</v>
+        <v>6.801973211782698</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783772894536892</v>
+        <v>6.783784989768318</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784491633860478</v>
+        <v>6.78451336207519</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775674472584828</v>
+        <v>6.775683729615968</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772296263744577</v>
+        <v>6.772298045169803</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768330013812967</v>
+        <v>6.76833303630324</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762275314152753</v>
+        <v>6.762284274011494</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752965918416016</v>
+        <v>6.752980340666754</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740874445948231</v>
+        <v>6.74089492422457</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728726512613685</v>
+        <v>6.728752003612929</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718555877886774</v>
+        <v>6.718581170765919</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712331001772581</v>
+        <v>6.712355407481285</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709506099246068</v>
+        <v>6.709227531408611</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707060437007591</v>
+        <v>6.70670658125799</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696509957846345</v>
+        <v>6.696345334627504</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.6834551245362</v>
+        <v>6.683306895500535</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.669710206756168</v>
+        <v>6.669731318885253</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.65066519801882</v>
+        <v>6.651058659106238</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.650568961371841</v>
+        <v>6.65091555309048</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.657545665713752</v>
+        <v>6.657694508271266</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.680137252005744</v>
+        <v>6.679539839230024</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.689904513696563</v>
+        <v>6.688650211167854</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.710113810527917</v>
+        <v>6.707462257748455</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.721891889135714</v>
+        <v>6.717456404561637</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.70053459524326</v>
+        <v>6.695470141072157</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.688319322590679</v>
+        <v>6.677936455322701</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141418463387144</v>
+        <v>7.141415552504386</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151519505381103</v>
+        <v>7.151514637697239</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155033771260507</v>
+        <v>7.155028975172424</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16838250235882</v>
+        <v>7.168377123447214</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183351339191703</v>
+        <v>7.183346241519576</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195309157856868</v>
+        <v>7.195304413682793</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197604051042938</v>
+        <v>7.197599761388592</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192156525359611</v>
+        <v>7.192152729086265</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175530516929959</v>
+        <v>7.175532676833216</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180435906814895</v>
+        <v>7.180441259007168</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184467406296251</v>
+        <v>7.184472429255454</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189566311681774</v>
+        <v>7.189571275240483</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18342668354666</v>
+        <v>7.18343564640097</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182618172704537</v>
+        <v>7.182628640674954</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183661335239387</v>
+        <v>7.183670087768125</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168929772448678</v>
+        <v>7.168937383200264</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155603758501197</v>
+        <v>7.155615074261391</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148449520530606</v>
+        <v>7.148462451806994</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144337867489604</v>
+        <v>7.144354007809877</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124342729318518</v>
+        <v>7.124355920837377</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111833680685598</v>
+        <v>7.111851614487829</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103298334426558</v>
+        <v>7.103318694316147</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075606061419811</v>
+        <v>7.0756289528303</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051016938312188</v>
+        <v>7.051040419866302</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049394280939584</v>
+        <v>7.049419149780254</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048022556554573</v>
+        <v>7.048053288171048</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055087881727576</v>
+        <v>7.055125594388999</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.0608999377846</v>
+        <v>7.060952075965084</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016294051053166</v>
+        <v>7.01634160628995</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968631898464677</v>
+        <v>6.968670758507754</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969224880654211</v>
+        <v>6.969262979736046</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949583754096478</v>
+        <v>6.949632907343077</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898741055592524</v>
+        <v>6.898768130183942</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862226267849222</v>
+        <v>6.862254729294225</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84783471967067</v>
+        <v>6.847858906131171</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823616211119842</v>
+        <v>6.823597181299268</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842196240777735</v>
+        <v>6.842171436496775</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855999527744522</v>
+        <v>6.855945918269352</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887592193578199</v>
+        <v>6.887566228010475</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890101347608432</v>
+        <v>6.89008349543162</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87736404072419</v>
+        <v>6.877333210393525</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872339819706929</v>
+        <v>6.872360105827751</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846257926055148</v>
+        <v>6.846269874669856</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842364524555299</v>
+        <v>6.842384486122574</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807056480593618</v>
+        <v>6.807027546443262</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823982584207513</v>
+        <v>6.823983981074065</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819219710281613</v>
+        <v>6.819240038162162</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813924441814453</v>
+        <v>6.813947730283395</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807978287564715</v>
+        <v>6.808005311778846</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803634072670082</v>
+        <v>6.803663756824757</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801973211782698</v>
+        <v>6.80200546778206</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783784989768318</v>
+        <v>6.78379685393726</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.78451336207519</v>
+        <v>6.784534695082393</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775683729615968</v>
+        <v>6.775692832477377</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772298045169803</v>
+        <v>6.772299810917759</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76833303630324</v>
+        <v>6.768335998481102</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762284274011494</v>
+        <v>6.762293034022802</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752980340666754</v>
+        <v>6.752994456167524</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74089492422457</v>
+        <v>6.740914982602419</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728752003612929</v>
+        <v>6.728777033802446</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718581170765919</v>
+        <v>6.718606064839831</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712355407481285</v>
+        <v>6.712379466270173</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709227531408611</v>
+        <v>6.708960525718272</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.70670658125799</v>
+        <v>6.706399560010246</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696345334627504</v>
+        <v>6.696266690608251</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683306895500535</v>
+        <v>6.683375136885671</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.669731318885253</v>
+        <v>6.670027567436156</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.651058659106238</v>
+        <v>6.651703255822214</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.65091555309048</v>
+        <v>6.651432875523903</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.657694508271266</v>
+        <v>6.657891710969098</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.679539839230024</v>
+        <v>6.678875623142169</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.688650211167854</v>
+        <v>6.687116987515027</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.707462257748455</v>
+        <v>6.704310689717281</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.717456404561637</v>
+        <v>6.712199847321923</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.695470141072157</v>
+        <v>6.688599966196997</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.677936455322701</v>
+        <v>6.664546783869165</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141415552504386</v>
+        <v>7.141412697061936</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151514637697239</v>
+        <v>7.151509862485673</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155028975172424</v>
+        <v>7.15502426967311</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168377123447214</v>
+        <v>7.168371846039551</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183346241519576</v>
+        <v>7.183341240100351</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195304413682793</v>
+        <v>7.195299759139106</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197599761388592</v>
+        <v>7.197595552786106</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192152729086265</v>
+        <v>7.192149004524347</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175532676833216</v>
+        <v>7.175534793526174</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180441259007168</v>
+        <v>7.180446508720504</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184472429255454</v>
+        <v>7.184477356113372</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189571275240483</v>
+        <v>7.189576143887551</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18343564640097</v>
+        <v>7.183444437954593</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182628640674954</v>
+        <v>7.182638909265869</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183670087768125</v>
+        <v>7.183678673598232</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168937383200264</v>
+        <v>7.168944847313646</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155615074261391</v>
+        <v>7.155626172860588</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148462451806994</v>
+        <v>7.148475135140631</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144354007809877</v>
+        <v>7.144369840472853</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124355920837377</v>
+        <v>7.124368858817023</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111851614487829</v>
+        <v>7.111869207566789</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103318694316147</v>
+        <v>7.103338670187703</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.0756289528303</v>
+        <v>7.075651417238852</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051040419866302</v>
+        <v>7.051063463664331</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049419149780254</v>
+        <v>7.049443552861441</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048053288171048</v>
+        <v>7.04808343872489</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055125594388999</v>
+        <v>7.055162590794574</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060952075965084</v>
+        <v>7.061003220199354</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.01634160628995</v>
+        <v>7.016388248531008</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968670758507754</v>
+        <v>6.968708880435909</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969262979736046</v>
+        <v>6.969300362626853</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949632907343077</v>
+        <v>6.949681165720007</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898768130183942</v>
+        <v>6.898794718432288</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862254729294225</v>
+        <v>6.862282682552578</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847858906131171</v>
+        <v>6.847882676065679</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823597181299268</v>
+        <v>6.823578528537434</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842171436496775</v>
+        <v>6.842147117094797</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855945918269352</v>
+        <v>6.855893310343509</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887566228010475</v>
+        <v>6.887540746534551</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89008349543162</v>
+        <v>6.890065963213342</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877333210393525</v>
+        <v>6.877302933262689</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872360105827751</v>
+        <v>6.872380014557994</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846269874669856</v>
+        <v>6.846281608318403</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842384486122574</v>
+        <v>6.842404087366129</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807027546443262</v>
+        <v>6.80699912604468</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823983981074065</v>
+        <v>6.823985335480987</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819240038162162</v>
+        <v>6.819259968097364</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813947730283395</v>
+        <v>6.813970564221312</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808005311778846</v>
+        <v>6.808031816109032</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803663756824757</v>
+        <v>6.803692880124816</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.80200546778206</v>
+        <v>6.802037129837563</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.78379685393726</v>
+        <v>6.783808493575973</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784534695082393</v>
+        <v>6.784555643513762</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775692832477377</v>
+        <v>6.775701784908835</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772299810917759</v>
+        <v>6.772301560953496</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768335998481102</v>
+        <v>6.76833890217147</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762293034022802</v>
+        <v>6.76230160062811</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752994456167524</v>
+        <v>6.753008274321536</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740914982602419</v>
+        <v>6.74093463348113</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728777033802446</v>
+        <v>6.728801615143684</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718606064839831</v>
+        <v>6.71863056882583</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712379466270173</v>
+        <v>6.712403184586694</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708960525718272</v>
+        <v>6.7086625790542</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.706399560010246</v>
+        <v>6.706050169608854</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696266690608251</v>
+        <v>6.69612317886761</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683375136885671</v>
+        <v>6.683375940746652</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.670027567436156</v>
+        <v>6.670240281131212</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.651703255822214</v>
+        <v>6.652240397604427</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.651432875523903</v>
+        <v>6.651839802296227</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.657891710969098</v>
+        <v>6.657990089375</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.678875623142169</v>
+        <v>6.678156800815472</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.687116987515027</v>
+        <v>6.685594499649799</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.704310689717281</v>
+        <v>6.701330977775843</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.712199847321923</v>
+        <v>6.707428678130535</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.688599966196997</v>
+        <v>6.682832947729257</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.664546783869165</v>
+        <v>6.65620240992366</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141412697061936</v>
+        <v>7.141409895490918</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151509862485673</v>
+        <v>7.151505177136306</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15502426967311</v>
+        <v>7.155019652220416</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168371846039551</v>
+        <v>7.168366667290042</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183341240100351</v>
+        <v>7.183336332233858</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195299759139106</v>
+        <v>7.195295191709931</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197595552786106</v>
+        <v>7.197591422960132</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192149004524347</v>
+        <v>7.192145349661202</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175534793526174</v>
+        <v>7.175536868289477</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180446508720504</v>
+        <v>7.180451658869833</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184477356113372</v>
+        <v>7.184482189601473</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189576143887551</v>
+        <v>7.189580920319155</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183444437954593</v>
+        <v>7.183453063070889</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182638909265869</v>
+        <v>7.182648984117969</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183678673598232</v>
+        <v>7.183687097446221</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168944847313646</v>
+        <v>7.168952168984488</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155626172860588</v>
+        <v>7.155637060487491</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148475135140631</v>
+        <v>7.148487577589924</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144369840472853</v>
+        <v>7.144385374188355</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124368858817023</v>
+        <v>7.124381550493292</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111869207566789</v>
+        <v>7.11188646953371</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103338670187703</v>
+        <v>7.103358272793795</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075651417238852</v>
+        <v>7.075673466470935</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051063463664331</v>
+        <v>7.051086081821587</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049443552861441</v>
+        <v>7.049467503134119</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.04808343872489</v>
+        <v>7.048113024528426</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055162590794574</v>
+        <v>7.055198891137691</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061003220199354</v>
+        <v>7.061053398606111</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016388248531008</v>
+        <v>7.016434003789286</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968708880435909</v>
+        <v>6.968746285036772</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969300362626853</v>
+        <v>6.969337049284102</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949681165720007</v>
+        <v>6.949728553377073</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898794718432288</v>
+        <v>6.898820833273524</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862282682552578</v>
+        <v>6.862310141052157</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847882676065679</v>
+        <v>6.847906040024482</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823578528537434</v>
+        <v>6.823560241778891</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842147117094797</v>
+        <v>6.842123268533602</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855893310343509</v>
+        <v>6.855841676198958</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887540746534551</v>
+        <v>6.887515735758629</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890065963213342</v>
+        <v>6.89004874247547</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877302933262689</v>
+        <v>6.877273194632641</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872380014557994</v>
+        <v>6.872399556327355</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846281608318403</v>
+        <v>6.846293132739306</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842404087366129</v>
+        <v>6.842423337945114</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.80699912604468</v>
+        <v>6.806971205909733</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823985335480987</v>
+        <v>6.823986649061494</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819259968097364</v>
+        <v>6.819279511625531</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813970564221312</v>
+        <v>6.813992956764962</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808031816109032</v>
+        <v>6.808057815377079</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803692880124816</v>
+        <v>6.803721458281816</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802037129837563</v>
+        <v>6.80206821415972</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783808493575973</v>
+        <v>6.783819914973751</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784555643513762</v>
+        <v>6.784576217625087</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775701784908835</v>
+        <v>6.775710590533373</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772301560953496</v>
+        <v>6.772303295259775</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76833890217147</v>
+        <v>6.76834174912525</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.76230160062811</v>
+        <v>6.762309980000615</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753008274321536</v>
+        <v>6.753021804160677</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74093463348113</v>
+        <v>6.740953888789214</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728801615143684</v>
+        <v>6.728825759203467</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.71863056882583</v>
+        <v>6.71865469121561</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712403184586694</v>
+        <v>6.712426568758935</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.7086625790542</v>
+        <v>6.708694831161242</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.706050169608854</v>
+        <v>6.705899710300693</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.69612317886761</v>
+        <v>6.696066538506453</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683375940746652</v>
+        <v>6.683666976580454</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.670240281131212</v>
+        <v>6.670670434767126</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.652240397604427</v>
+        <v>6.65299420021157</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.651839802296227</v>
+        <v>6.652508069816724</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.657990089375</v>
+        <v>6.65839022553406</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.678156800815472</v>
+        <v>6.677836961523179</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.685594499649799</v>
+        <v>6.684813940748279</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.701330977775843</v>
+        <v>6.699309687193646</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.707428678130535</v>
+        <v>6.704143323616338</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.682832947729257</v>
+        <v>6.679607433537284</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,15 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.65620240992366</v>
+        <v>6.653985739451643</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>6.640081485753838</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141409895490918</v>
+        <v>7.141407146281095</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151505177136306</v>
+        <v>7.151500579136336</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155019652220416</v>
+        <v>7.155015120366417</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168366667290042</v>
+        <v>7.168361584458273</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183336332233858</v>
+        <v>7.183331515319973</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195295191709931</v>
+        <v>7.195290708972665</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197591422960132</v>
+        <v>7.197587369719694</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192145349661202</v>
+        <v>7.192141762558792</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175536868289477</v>
+        <v>7.175538902353781</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180451658869833</v>
+        <v>7.180456712260584</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184482189601473</v>
+        <v>7.184486932348702</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189580920319155</v>
+        <v>7.189585607130321</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183453063070889</v>
+        <v>7.183461526430886</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182648984117969</v>
+        <v>7.182658870661223</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183687097446221</v>
+        <v>7.183695363852374</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168952168984488</v>
+        <v>7.168959352249968</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155637060487491</v>
+        <v>7.155647743097981</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148487577589924</v>
+        <v>7.148499785948053</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144385374188355</v>
+        <v>7.144400617340649</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124381550493292</v>
+        <v>7.124394002829424</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11188646953371</v>
+        <v>7.111903409641972</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103358272793795</v>
+        <v>7.103377512489667</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075673466470935</v>
+        <v>7.075695111919776</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051086081821587</v>
+        <v>7.051108286010876</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049467503134119</v>
+        <v>7.049491013073972</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048113024528426</v>
+        <v>7.048142061289524</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055198891137691</v>
+        <v>7.055234514860454</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061053398606111</v>
+        <v>7.061102638254627</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016434003789286</v>
+        <v>7.016478897099907</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968746285036772</v>
+        <v>6.968782992326277</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969337049284102</v>
+        <v>6.969373058932394</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949728553377073</v>
+        <v>6.949775093605393</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898820833273524</v>
+        <v>6.898846487190844</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862310141052157</v>
+        <v>6.862337117754278</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847906040024482</v>
+        <v>6.847929008209211</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823560241778891</v>
+        <v>6.823542310394775</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842123268533602</v>
+        <v>6.842099877310243</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855841676198958</v>
+        <v>6.855790989083308</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887515735758629</v>
+        <v>6.887491182779577</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89004874247547</v>
+        <v>6.890031825034955</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877273194632641</v>
+        <v>6.877243980318312</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872399556327355</v>
+        <v>6.872418741184866</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846293132739306</v>
+        <v>6.846304453469016</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842423337945114</v>
+        <v>6.842442247176828</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806971205909733</v>
+        <v>6.806943773015486</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823986649061494</v>
+        <v>6.823987923372266</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819279511625531</v>
+        <v>6.819298679844383</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813992956764962</v>
+        <v>6.814014920551184</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808057815377079</v>
+        <v>6.808083323848031</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803721458281816</v>
+        <v>6.803749506427176</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.80206821415972</v>
+        <v>6.802098736376123</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783819914973751</v>
+        <v>6.783831124188087</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784576217625087</v>
+        <v>6.784596427312644</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775710590533373</v>
+        <v>6.775719252861654</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772303295259775</v>
+        <v>6.77230501383557</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76834174912525</v>
+        <v>6.768344541023092</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762309980000615</v>
+        <v>6.76231817805885</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753021804160677</v>
+        <v>6.753035054363282</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740953888789214</v>
+        <v>6.740972760005938</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728825759203467</v>
+        <v>6.728849477169375</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.71865469121561</v>
+        <v>6.718678440281024</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712426568758935</v>
+        <v>6.712449624995932</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708694831161242</v>
+        <v>6.70872665308547</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.705899710300693</v>
+        <v>6.705974341168623</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696066538506453</v>
+        <v>6.696282264801777</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683666976580454</v>
+        <v>6.684232128862096</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.670670434767126</v>
+        <v>6.671488598168011</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.65299420021157</v>
+        <v>6.654120038941938</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.652508069816724</v>
+        <v>6.653586772635271</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.65839022553406</v>
+        <v>6.659250895560753</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.677836961523179</v>
+        <v>6.678086545921783</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.684813940748279</v>
+        <v>6.684735455778675</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.699309687193646</v>
+        <v>6.698267407391675</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.704143323616338</v>
+        <v>6.702247845366867</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.679607433537284</v>
+        <v>6.678473004651669</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.653985739451643</v>
+        <v>6.655337510500724</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.640081485753838</v>
+        <v>6.650439402876115</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141407146281095</v>
+        <v>7.141404447978161</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151500579136336</v>
+        <v>7.151496066065786</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155015120366417</v>
+        <v>7.155010671753091</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168361584458273</v>
+        <v>7.168356594904376</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183331515319973</v>
+        <v>7.183326786854026</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195290708972665</v>
+        <v>7.195286308593698</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197587369719694</v>
+        <v>7.197583390954303</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192141762558792</v>
+        <v>7.192138241350257</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175538902353781</v>
+        <v>7.175540896902141</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180456712260584</v>
+        <v>7.180461671593784</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184486932348702</v>
+        <v>7.184491586886232</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189585607130321</v>
+        <v>7.18959020681962</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183461526430886</v>
+        <v>7.183469832541741</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182658870661223</v>
+        <v>7.182668574124627</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183695363852374</v>
+        <v>7.183703477188896</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168959352249968</v>
+        <v>7.168966400996194</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155647743097981</v>
+        <v>7.155658226425954</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148499785948053</v>
+        <v>7.148511766755322</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144400617340649</v>
+        <v>7.144415578003507</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124394002829424</v>
+        <v>7.124406222528771</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111903409641972</v>
+        <v>7.111920036803596</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103377512489667</v>
+        <v>7.103396399251405</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075695111919776</v>
+        <v>7.075716364565928</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051108286010876</v>
+        <v>7.051130087482499</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049491013073972</v>
+        <v>7.049514094702968</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048142061289524</v>
+        <v>7.048170564139339</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055234514860454</v>
+        <v>7.055269480688267</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061102638254627</v>
+        <v>7.061150965213191</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016478897099907</v>
+        <v>7.016522952565619</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968782992326277</v>
+        <v>6.968819021584052</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969373058932394</v>
+        <v>6.969408410096717</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949775093605393</v>
+        <v>6.949820808875097</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898846487190844</v>
+        <v>6.898871692234222</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862337117754278</v>
+        <v>6.862363625173664</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847929008209211</v>
+        <v>6.847951590486909</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823542310394775</v>
+        <v>6.823524724162489</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842099877310243</v>
+        <v>6.842076930431826</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855790989083308</v>
+        <v>6.855741223213878</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887491182779577</v>
+        <v>6.887467075160872</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890031825034955</v>
+        <v>6.890015202991183</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877243980318312</v>
+        <v>6.877215276626425</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872418741184866</v>
+        <v>6.872437578816111</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846304453469016</v>
+        <v>6.846315575850723</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842442247176828</v>
+        <v>6.842460824051699</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806943773015486</v>
+        <v>6.806916814784452</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823987923372266</v>
+        <v>6.823989159897671</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819298679844383</v>
+        <v>6.819317483431822</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814014920551184</v>
+        <v>6.814036467740374</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808083323848031</v>
+        <v>6.808108355255985</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803749506427176</v>
+        <v>6.803777039138653</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802098736376123</v>
+        <v>6.802128711557348</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783831124188087</v>
+        <v>6.783842127055209</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784596427312644</v>
+        <v>6.784616282128722</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775719252861654</v>
+        <v>6.77572777529612</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.77230501383557</v>
+        <v>6.772306716694672</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768344541023092</v>
+        <v>6.768347279478912</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.76231817805885</v>
+        <v>6.762326200479469</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753035054363282</v>
+        <v>6.753048033270916</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740972760005938</v>
+        <v>6.740991258181806</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728849477169375</v>
+        <v>6.728872779864451</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718678440281024</v>
+        <v>6.718701824079811</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712449624995932</v>
+        <v>6.712472359388252</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.70872665308547</v>
+        <v>6.708758052273863</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.705974341168623</v>
+        <v>6.706259571592748</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696282264801777</v>
+        <v>6.696756819674216</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.684232128862096</v>
+        <v>6.68506098283593</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.671488598168011</v>
+        <v>6.67257477249003</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.654120038941938</v>
+        <v>6.655606263179914</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.653586772635271</v>
+        <v>6.655134270203073</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.659250895560753</v>
+        <v>6.660694344902049</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.678086545921783</v>
+        <v>6.679085806151379</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.684735455778675</v>
+        <v>6.685599599641664</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.698267407391675</v>
+        <v>6.698586660217071</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.702247845366867</v>
+        <v>6.70221819368626</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.678473004651669</v>
+        <v>6.680030733763079</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.655337510500724</v>
+        <v>6.660796040761818</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.650439402876115</v>
+        <v>6.665863486932686</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141404447978161</v>
+        <v>7.141401799181168</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151496066065786</v>
+        <v>7.151491635593243</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155010671753091</v>
+        <v>7.155006304108219</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168356594904376</v>
+        <v>7.168351696084458</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183326786854026</v>
+        <v>7.183322144422462</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195286308593698</v>
+        <v>7.195281988324352</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197583390954303</v>
+        <v>7.197579484630301</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192138241350257</v>
+        <v>7.192134784236682</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175540896902141</v>
+        <v>7.175542853072304</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180461671593784</v>
+        <v>7.180466539470872</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184491586886232</v>
+        <v>7.184496155651973</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18959020681962</v>
+        <v>7.189594721793615</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183469832541741</v>
+        <v>7.183477985744736</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182668574124627</v>
+        <v>7.182678099545405</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183703477188896</v>
+        <v>7.183711441667607</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168966400996194</v>
+        <v>7.168973318965198</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155658226425954</v>
+        <v>7.155668515993559</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148511766755322</v>
+        <v>7.148523526310791</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144415578003507</v>
+        <v>7.144430263954437</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124406222528771</v>
+        <v>7.124418216046802</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111920036803596</v>
+        <v>7.111936359604835</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103396399251405</v>
+        <v>7.103414942693111</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075716364565928</v>
+        <v>7.075737234995745</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051130087482499</v>
+        <v>7.051151497083182</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049514094702968</v>
+        <v>7.049536759609785</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048170564139339</v>
+        <v>7.048198547658499</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055269480688267</v>
+        <v>7.055303806662518</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061150965213191</v>
+        <v>7.061198404594895</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016522952565619</v>
+        <v>7.01656619339977</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968819021584052</v>
+        <v>6.968854391386902</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969408410096717</v>
+        <v>6.969443120633894</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949820808875097</v>
+        <v>6.949865720871081</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898871692234222</v>
+        <v>6.898896460038944</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862363625173664</v>
+        <v>6.862389675397413</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847951590486909</v>
+        <v>6.847973796403405</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823524724162489</v>
+        <v>6.823507473246529</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842076930431826</v>
+        <v>6.842054415391708</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855741223213878</v>
+        <v>6.85569235373421</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887467075160872</v>
+        <v>6.887443400911738</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890015202991183</v>
+        <v>6.889998868713978</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877215276626425</v>
+        <v>6.877187070334468</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872437578816111</v>
+        <v>6.872456078559487</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846315575850723</v>
+        <v>6.846326505042693</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842460824051699</v>
+        <v>6.84247907724747</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806916814784452</v>
+        <v>6.80689031906584</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823989159897671</v>
+        <v>6.823990360053735</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819317483431822</v>
+        <v>6.819335932665547</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814036467740374</v>
+        <v>6.814057610038681</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808108355255985</v>
+        <v>6.808132922828531</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803777039138653</v>
+        <v>6.803804070465381</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802128711557348</v>
+        <v>6.802158154241471</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783842127055209</v>
+        <v>6.783852929200054</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784616282128722</v>
+        <v>6.784635791296346</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.77572777529612</v>
+        <v>6.775736161134993</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772306716694672</v>
+        <v>6.772308403864393</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768347279478912</v>
+        <v>6.76834996604321</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762326200479469</v>
+        <v>6.762334052709278</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753048033270916</v>
+        <v>6.753060748904214</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740991258181806</v>
+        <v>6.741009393957909</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728872779864451</v>
+        <v>6.728895677761274</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718701824079811</v>
+        <v>6.718724850461229</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712472359388252</v>
+        <v>6.712494777908734</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708758052273863</v>
+        <v>6.708789036048894</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.706259571592748</v>
+        <v>6.706531761673192</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696756819674216</v>
+        <v>6.697236351249137</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.68506098283593</v>
+        <v>6.685858710505487</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.67257477249003</v>
+        <v>6.673615837749852</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.655606263179914</v>
+        <v>6.657025970467805</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.655134270203073</v>
+        <v>6.65660682652401</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.660694344902049</v>
+        <v>6.662062821531137</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.679085806151379</v>
+        <v>6.680025085714671</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.685599599641664</v>
+        <v>6.686403118168757</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.698586660217071</v>
+        <v>6.698871767207986</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.70221819368626</v>
+        <v>6.702179196790013</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.680030733763079</v>
+        <v>6.681360501993566</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.660796040761818</v>
+        <v>6.665006516465247</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.665863486932686</v>
+        <v>6.67350345876411</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.706531761673192</v>
+        <v>6.706718338663423</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.697236351249137</v>
+        <v>6.697454616757362</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.685858710505487</v>
+        <v>6.686090753184923</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.673615837749852</v>
+        <v>6.673887824896862</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.657025970467805</v>
+        <v>6.657343911190744</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.65660682652401</v>
+        <v>6.656973740834638</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.662062821531137</v>
+        <v>6.662480943792211</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.680025085714671</v>
+        <v>6.680514929858749</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.686403118168757</v>
+        <v>6.686984319953719</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.698871767207986</v>
+        <v>6.699608705496088</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.702179196790013</v>
+        <v>6.703113467079223</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.681360501993566</v>
+        <v>6.68270404537301</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.665006516465247</v>
+        <v>6.667210967139674</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.67350345876411</v>
+        <v>6.678441521682383</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141401799181168</v>
+        <v>7.1413991985401</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151491635593243</v>
+        <v>7.151487285471848</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155006304108219</v>
+        <v>7.155002015241526</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168351696084458</v>
+        <v>7.168346885546281</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183322144422462</v>
+        <v>7.183317585698733</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195281988324352</v>
+        <v>7.19527774599707</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197579484630301</v>
+        <v>7.197575648787394</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192134784236682</v>
+        <v>7.192131389484038</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175542853072304</v>
+        <v>7.175544771958844</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180466539470872</v>
+        <v>7.180471318398234</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184496155651973</v>
+        <v>7.184500640994838</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189594721793615</v>
+        <v>7.18959915437105</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183477985744736</v>
+        <v>7.18348599022284</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182678099545405</v>
+        <v>7.182687451777737</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183711441667607</v>
+        <v>7.183719261347242</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168973318965198</v>
+        <v>7.168980109761543</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155668515993559</v>
+        <v>7.155678617120882</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148523526310791</v>
+        <v>7.148535070683304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144430263954437</v>
+        <v>7.144444682688154</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124418216046802</v>
+        <v>7.124429989602453</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111936359604835</v>
+        <v>7.111952386320898</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103414942693111</v>
+        <v>7.103433152083165</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075737234995745</v>
+        <v>7.075757733418914</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051151497083182</v>
+        <v>7.051172525273978</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049536759609785</v>
+        <v>7.049559018969134</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048198547658499</v>
+        <v>7.048226025901912</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055303806662518</v>
+        <v>7.055337510171514</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061198404594895</v>
+        <v>7.061244980600948</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.01656619339977</v>
+        <v>7.016608641966902</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968854391386902</v>
+        <v>6.968889119640489</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969443120633894</v>
+        <v>6.969477207762373</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949865720871081</v>
+        <v>6.949909850526915</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898896460038944</v>
+        <v>6.898920801843229</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862389675397413</v>
+        <v>6.862415280103021</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847973796403405</v>
+        <v>6.847995635196098</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823507473246529</v>
+        <v>6.823490548180395</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842054415391708</v>
+        <v>6.842032320147014</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.85569235373421</v>
+        <v>6.855644356672904</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887443400911738</v>
+        <v>6.887420148467378</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889998868713978</v>
+        <v>6.889982814832212</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877187070334468</v>
+        <v>6.877159348670736</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872456078559487</v>
+        <v>6.87247424942163</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846326505042693</v>
+        <v>6.846337246026196</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.84247907724747</v>
+        <v>6.842497015142671</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.80689031906584</v>
+        <v>6.806864274117725</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823990360053735</v>
+        <v>6.823991525191849</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819335932665547</v>
+        <v>6.819354037441593</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814057610038681</v>
+        <v>6.814078358718962</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808132922828531</v>
+        <v>6.808157039309828</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803804070465381</v>
+        <v>6.803830613951565</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802158154241471</v>
+        <v>6.802187078457318</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783852929200054</v>
+        <v>6.783863536045706</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784635791296346</v>
+        <v>6.784654963723272</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775736161134993</v>
+        <v>6.775744413576108</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772308403864393</v>
+        <v>6.772310075384398</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76834996604321</v>
+        <v>6.768352602206176</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762334052709278</v>
+        <v>6.76234173997655</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753060748904214</v>
+        <v>6.753073208977866</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741009393957909</v>
+        <v>6.741027177584299</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728895677761274</v>
+        <v>6.728918180995426</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718724850461229</v>
+        <v>6.718747527071606</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712494777908734</v>
+        <v>6.71251688641345</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708789036048894</v>
+        <v>6.708819611608382</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.706718338663423</v>
+        <v>6.707157033571299</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.697454616757362</v>
+        <v>6.69812242049143</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.686090753184923</v>
+        <v>6.687076663974546</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.673887824896862</v>
+        <v>6.675144957395132</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.657343911190744</v>
+        <v>6.659005001423261</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.656973740834638</v>
+        <v>6.65872628988213</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.662480943792211</v>
+        <v>6.664178178961257</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.680514929858749</v>
+        <v>6.681864286685699</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.686984319953719</v>
+        <v>6.688281334209852</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.699608705496088</v>
+        <v>6.700554334037832</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.703113467079223</v>
+        <v>6.703926266156285</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.68270404537301</v>
+        <v>6.685035341978793</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.667210967139674</v>
+        <v>6.672332872581479</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.678441521682383</v>
+        <v>6.685981788764625</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.1413991985401</v>
+        <v>7.141396644753593</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151487285471848</v>
+        <v>7.151483013535501</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155002015241526</v>
+        <v>7.154997803041017</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168346885546281</v>
+        <v>7.168342160925167</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183317585698733</v>
+        <v>7.183313108439411</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19527774599707</v>
+        <v>7.19527357952178</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197575648787394</v>
+        <v>7.197571881535373</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192131389484038</v>
+        <v>7.192128055420272</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175544771958844</v>
+        <v>7.175546654615192</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180471318398234</v>
+        <v>7.180476010791521</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184500640994838</v>
+        <v>7.184505045178753</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18959915437105</v>
+        <v>7.189603506786826</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18348599022284</v>
+        <v>7.18349385000786</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182687451777737</v>
+        <v>7.182696635500971</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183719261347242</v>
+        <v>7.183726940140343</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168980109761543</v>
+        <v>7.168986776858595</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155678617120882</v>
+        <v>7.155688534935102</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148535070683304</v>
+        <v>7.148546405721901</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144444682688154</v>
+        <v>7.144458841429304</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124429989602453</v>
+        <v>7.124441549188859</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111952386320898</v>
+        <v>7.111968124929918</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103433152083165</v>
+        <v>7.103451036359605</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075757733418914</v>
+        <v>7.07577786968504</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051172525273978</v>
+        <v>7.051193182147256</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049559018969134</v>
+        <v>7.049580883560079</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048226025901912</v>
+        <v>7.048253012422216</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055337510171514</v>
+        <v>7.055370607979723</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061244980600948</v>
+        <v>7.061290716561622</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016608641966902</v>
+        <v>7.016650319821171</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968889119640489</v>
+        <v>6.968923223609309</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969477207762373</v>
+        <v>6.969510688090438</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949909850526915</v>
+        <v>6.949953218056995</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898920801843229</v>
+        <v>6.898944728504942</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862415280103021</v>
+        <v>6.862440450575479</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847995635196098</v>
+        <v>6.848017115806103</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823490548180395</v>
+        <v>6.82347393984949</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842032320147014</v>
+        <v>6.8420106330974</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855644356672904</v>
+        <v>6.855597208904624</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887420148467378</v>
+        <v>6.887397306670249</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889982814832212</v>
+        <v>6.889967034222956</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877159348670736</v>
+        <v>6.87713209929535</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.87247424942163</v>
+        <v>6.872492100092003</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846337246026196</v>
+        <v>6.846347803612996</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842497015142671</v>
+        <v>6.842514645829392</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806864274117725</v>
+        <v>6.806838668590106</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823991525191849</v>
+        <v>6.823992656602249</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819354037441593</v>
+        <v>6.819371807291825</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814078358718962</v>
+        <v>6.814098724640587</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808157039309828</v>
+        <v>6.808180716982443</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803830613951565</v>
+        <v>6.803856682658918</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802187078457318</v>
+        <v>6.802215497746506</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783863536045706</v>
+        <v>6.783873952822336</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784654963723272</v>
+        <v>6.784673808015268</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775744413576108</v>
+        <v>6.775752535720577</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772310075384398</v>
+        <v>6.772311731305603</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768352602206176</v>
+        <v>6.768355189400634</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.76234173997655</v>
+        <v>6.762349267301708</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753073208977866</v>
+        <v>6.753085420914779</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741027177584299</v>
+        <v>6.741044618937382</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728918180995426</v>
+        <v>6.728940299378364</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718747527071606</v>
+        <v>6.718769861359791</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.71251688641345</v>
+        <v>6.7125386906428</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708819611608382</v>
+        <v>6.70884978602559</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707157033571299</v>
+        <v>6.707580850437585</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.69812242049143</v>
+        <v>6.698772145941318</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.687076663974546</v>
+        <v>6.688030337106412</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.675144957395132</v>
+        <v>6.67635933069728</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.659005001423261</v>
+        <v>6.660603384251098</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.65872628988213</v>
+        <v>6.660402381027426</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.664178178961257</v>
+        <v>6.665787661967787</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.681864286685699</v>
+        <v>6.68311970352789</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.688281334209852</v>
+        <v>6.689453867599742</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.700554334037832</v>
+        <v>6.701336040521999</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.703926266156285</v>
+        <v>6.704513682998472</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.685035341978793</v>
+        <v>6.686830796092242</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.672332872581479</v>
+        <v>6.676075335868036</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.685981788764625</v>
+        <v>6.690133082887874</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141396644753593</v>
+        <v>7.141394136566749</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151483013535501</v>
+        <v>7.151478817695259</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154997803041017</v>
+        <v>7.15499366546951</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168342160925167</v>
+        <v>7.168337519940132</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183313108439411</v>
+        <v>7.183308710480521</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19527357952178</v>
+        <v>7.195269486882465</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197571881535373</v>
+        <v>7.197568181051015</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192128055420272</v>
+        <v>7.192124780432577</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175546654615192</v>
+        <v>7.175548502055543</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180476010791521</v>
+        <v>7.180480618979706</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184505045178753</v>
+        <v>7.184509370386467</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189603506786826</v>
+        <v>7.189607781195747</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18349385000786</v>
+        <v>7.183501568987202</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182696635500971</v>
+        <v>7.182705655227442</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183726940140343</v>
+        <v>7.183734481819771</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168986776858595</v>
+        <v>7.168993323604411</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155688534935102</v>
+        <v>7.155698274379152</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148546405721901</v>
+        <v>7.148557537065669</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144458841429304</v>
+        <v>7.144472747144517</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124441549188859</v>
+        <v>7.124452900583495</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111968124929918</v>
+        <v>7.111983583126143</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103451036359605</v>
+        <v>7.103468604144709</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07577786968504</v>
+        <v>7.075797653299366</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051193182147256</v>
+        <v>7.051213477442776</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049580883560079</v>
+        <v>7.049602363783358</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048253012422216</v>
+        <v>7.048279520292018</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055370607979723</v>
+        <v>7.055403116255498</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061290716561622</v>
+        <v>7.061335634975069</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016650319821171</v>
+        <v>7.016691247742672</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968923223609309</v>
+        <v>6.968956719945068</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969510688090438</v>
+        <v>6.969543577642926</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949953218056995</v>
+        <v>6.949995842987089</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898944728504942</v>
+        <v>6.898968250517486</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862440450575479</v>
+        <v>6.86246519772356</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848017115806103</v>
+        <v>6.848038246889896</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82347393984949</v>
+        <v>6.823457639474965</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.8420106330974</v>
+        <v>6.841989343064949</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855597208904624</v>
+        <v>6.85555088811315</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887397306670249</v>
+        <v>6.887374864752328</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889967034222956</v>
+        <v>6.889951520001205</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87713209929535</v>
+        <v>6.877105310282253</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872492100092003</v>
+        <v>6.872509638956745</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846347803612996</v>
+        <v>6.846358182452521</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842514645829392</v>
+        <v>6.842531977125413</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806838668590106</v>
+        <v>6.806813491508793</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823992656602249</v>
+        <v>6.823993755517277</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819371807291825</v>
+        <v>6.819389251400514</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814098724640587</v>
+        <v>6.814118718268183</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808180716982443</v>
+        <v>6.808203967688012</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803856682658918</v>
+        <v>6.803882289187915</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802215497746506</v>
+        <v>6.802243425184351</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783873952822336</v>
+        <v>6.783884184575678</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784673808015268</v>
+        <v>6.784692332488733</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775752535720577</v>
+        <v>6.775760530576305</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772311731305603</v>
+        <v>6.772313371689165</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768355189400634</v>
+        <v>6.768357729004806</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762349267301708</v>
+        <v>6.762356639507388</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753085420914779</v>
+        <v>6.753097391859477</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741044618937382</v>
+        <v>6.741061727536419</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728940299378364</v>
+        <v>6.728962042409761</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718769861359791</v>
+        <v>6.718791860582511</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.7125386906428</v>
+        <v>6.712560196222746</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.70884978602559</v>
+        <v>6.708879566249578</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707580850437585</v>
+        <v>6.707615872151276</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.698772145941318</v>
+        <v>6.698925990223907</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.688030337106412</v>
+        <v>6.688447094381174</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.67635933069728</v>
+        <v>6.677179033038747</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.660603384251098</v>
+        <v>6.662149868355489</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.660402381027426</v>
+        <v>6.662129397198909</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.665787661967787</v>
+        <v>6.667629847350653</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.68311970352789</v>
+        <v>6.684833258869068</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.689453867599742</v>
+        <v>6.691332892911076</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.701336040521999</v>
+        <v>6.703151346672086</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.704513682998472</v>
+        <v>6.707043660008756</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.686830796092242</v>
+        <v>6.69141809345105</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.676075335868036</v>
+        <v>6.683859645205255</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,15 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.690133082887874</v>
+        <v>6.701216285600077</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>6.736475660600076</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141394136566749</v>
+        <v>7.141391672769084</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151478817695259</v>
+        <v>7.151474695935936</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15499366546951</v>
+        <v>7.154989600561365</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168337519940132</v>
+        <v>7.168332960390211</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183308710480521</v>
+        <v>7.18330438973404</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195269486882465</v>
+        <v>7.195265466133912</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197568181051015</v>
+        <v>7.197564545575138</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192124780432577</v>
+        <v>7.192121562964781</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175548502055543</v>
+        <v>7.175550315256659</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180480618979706</v>
+        <v>7.180485145208934</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184509370386467</v>
+        <v>7.184513618723161</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189607781195747</v>
+        <v>7.189611979676086</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183501568987202</v>
+        <v>7.183509150910281</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182705655227442</v>
+        <v>7.182714515309844</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183734481819771</v>
+        <v>7.183741890024886</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168993323604411</v>
+        <v>7.168999753227354</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155698274379152</v>
+        <v>7.155707840219907</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148557537065669</v>
+        <v>7.14856847015308</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144472747144517</v>
+        <v>7.144486406553819</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124452900583495</v>
+        <v>7.124464049357795</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111983583126143</v>
+        <v>7.111998768332443</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103468604144709</v>
+        <v>7.103485863758793</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075797653299366</v>
+        <v>7.075817093437674</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051213477442776</v>
+        <v>7.051233420562937</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049602363783358</v>
+        <v>7.049623469677833</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048279520292018</v>
+        <v>7.048305562124934</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055403116255498</v>
+        <v>7.055435050597297</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061335634975069</v>
+        <v>7.061379757544024</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016691247742672</v>
+        <v>7.016731445771855</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968956719945068</v>
+        <v>6.9689896247136</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969543577642926</v>
+        <v>6.969575891886575</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949995842987089</v>
+        <v>6.950037744183325</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898968250517486</v>
+        <v>6.898991378024891</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.86246519772356</v>
+        <v>6.862489532095277</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848038246889896</v>
+        <v>6.848059036830376</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823457639474965</v>
+        <v>6.823441638598453</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841989343064949</v>
+        <v>6.841968439275167</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.85555088811315</v>
+        <v>6.855505372756341</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887374864752328</v>
+        <v>6.887352812318284</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889951520001205</v>
+        <v>6.889936265510085</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877105310282253</v>
+        <v>6.877078970102068</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872509638956745</v>
+        <v>6.872526874111771</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846358182452521</v>
+        <v>6.846368387038607</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842531977125413</v>
+        <v>6.842549016585711</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806813491508793</v>
+        <v>6.806788732260069</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823993755517277</v>
+        <v>6.823994823114447</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819389251400514</v>
+        <v>6.819406378619991</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814118718268183</v>
+        <v>6.81413834968936</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808203967688012</v>
+        <v>6.808226802846816</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803882289187915</v>
+        <v>6.803907445697928</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802243425184351</v>
+        <v>6.802270873399715</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783884184575678</v>
+        <v>6.783894236175051</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784692332488733</v>
+        <v>6.784710545182693</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775760530576305</v>
+        <v>6.775768401061361</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772313371689165</v>
+        <v>6.772314996605548</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768357729004806</v>
+        <v>6.768360222344903</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762356639507388</v>
+        <v>6.762363861227922</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753097391859477</v>
+        <v>6.753109128690772</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741061727536419</v>
+        <v>6.741078512559169</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728962042409761</v>
+        <v>6.728983419289299</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718791860582511</v>
+        <v>6.718813531809599</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712560196222746</v>
+        <v>6.712581408666178</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708879566249578</v>
+        <v>6.708908959105756</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707615872151276</v>
+        <v>6.707650554375038</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.698925990223907</v>
+        <v>6.699151763671782</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.688447094381174</v>
+        <v>6.688936913130028</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.677179033038747</v>
+        <v>6.678063552528602</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.662149868355489</v>
+        <v>6.663756224749154</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.662129397198909</v>
+        <v>6.66391638072999</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.667629847350653</v>
+        <v>6.669547383906609</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.684833258869068</v>
+        <v>6.686653770737826</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.691332892911076</v>
+        <v>6.693341228204062</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.703151346672086</v>
+        <v>6.705139433998522</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.707043660008756</v>
+        <v>6.709769006550252</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.69141809345105</v>
+        <v>6.696067416787052</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.683859645205255</v>
+        <v>6.691262323225322</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.701216285600077</v>
+        <v>6.71089307890532</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.736475660600076</v>
+        <v>6.746152453905319</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.699151763671782</v>
+        <v>6.699385008852012</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.688936913130028</v>
+        <v>6.689201014228741</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.678063552528602</v>
+        <v>6.678347392377468</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.663756224749154</v>
+        <v>6.663977352462</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.66391638072999</v>
+        <v>6.664228805423452</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.669547383906609</v>
+        <v>6.669925614461718</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.686653770737826</v>
+        <v>6.687118682327964</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.693341228204062</v>
+        <v>6.693913846332016</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.705139433998522</v>
+        <v>6.705849279864107</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.709769006550252</v>
+        <v>6.710698793159718</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.696067416787052</v>
+        <v>6.697355166846123</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.691262323225322</v>
+        <v>6.6931727889759</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.71089307890532</v>
+        <v>6.714066356183565</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.746152453905319</v>
+        <v>6.749325731183564</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141391672769084</v>
+        <v>7.141389252192583</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151474695935936</v>
+        <v>7.151470646312874</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154989600561365</v>
+        <v>7.154985606419348</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168332960390211</v>
+        <v>7.168328480150986</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.18330438973404</v>
+        <v>7.183300144184605</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195265466133912</v>
+        <v>7.19526151539864</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197564545575138</v>
+        <v>7.197560973409812</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192121562964781</v>
+        <v>7.192118401514888</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175550315256659</v>
+        <v>7.175552095159594</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180485145208934</v>
+        <v>7.180489591646186</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184513618723161</v>
+        <v>7.184517792219868</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189611979676086</v>
+        <v>7.189616104232949</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183509150910281</v>
+        <v>7.18351659939459</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182714515309844</v>
+        <v>7.182723219948238</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183741890024886</v>
+        <v>7.183749168267408</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168999753227354</v>
+        <v>7.169006068841391</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155707840219907</v>
+        <v>7.155717237055971</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14856847015308</v>
+        <v>7.148579210230821</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144486406553819</v>
+        <v>7.144499826141448</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124464049357795</v>
+        <v>7.124475000886253</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111998768332443</v>
+        <v>7.112013687712166</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103485863758793</v>
+        <v>7.103502823233319</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075817093437674</v>
+        <v>7.075836198960429</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051233420562937</v>
+        <v>7.051253020587251</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049623469677833</v>
+        <v>7.049644210936082</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048305562124934</v>
+        <v>7.048331150095541</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055435050597297</v>
+        <v>7.055466426058564</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061379757544024</v>
+        <v>7.061423105210627</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016731445771855</v>
+        <v>7.016770933242105</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.9689896247136</v>
+        <v>6.969021953420341</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969575891886575</v>
+        <v>6.969607645754055</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950037744183325</v>
+        <v>6.950078939879734</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898991378024891</v>
+        <v>6.899014120836192</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862489532095277</v>
+        <v>6.862513463892611</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848059036830376</v>
+        <v>6.848079493747436</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823441638598453</v>
+        <v>6.823425929067601</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841968439275167</v>
+        <v>6.841947911338988</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855505372756341</v>
+        <v>6.855460642032906</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887352812318284</v>
+        <v>6.8873311393295</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889936265510085</v>
+        <v>6.889921264311523</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877078970102068</v>
+        <v>6.877053067605814</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872526874111771</v>
+        <v>6.872543813375225</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846368387038607</v>
+        <v>6.846378421715967</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842549016585711</v>
+        <v>6.842565771513414</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806788732260069</v>
+        <v>6.8067643805761</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823994823114447</v>
+        <v>6.823995860519325</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819406378619991</v>
+        <v>6.819423197485482</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81413834968936</v>
+        <v>6.814157628631494</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808226802846816</v>
+        <v>6.808249233476311</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803907445697928</v>
+        <v>6.803932163926324</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802270873399715</v>
+        <v>6.802297854593855</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783894236175051</v>
+        <v>6.783904112320983</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784710545182693</v>
+        <v>6.784728453870221</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775768401061361</v>
+        <v>6.775776150007211</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772314996605548</v>
+        <v>6.772316606133668</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768360222344903</v>
+        <v>6.768362670697591</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762363861227922</v>
+        <v>6.762370936918303</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753109128690772</v>
+        <v>6.753120638033783</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741078512559169</v>
+        <v>6.74109498285675</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728983419289299</v>
+        <v>6.729004438927963</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718813531809599</v>
+        <v>6.718834881929146</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712581408666178</v>
+        <v>6.712602333374375</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708908959105756</v>
+        <v>6.70893797129662</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707650554375038</v>
+        <v>6.707684899611091</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.699385008852012</v>
+        <v>6.699610959813155</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.689201014228741</v>
+        <v>6.689682200171564</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.678347392377468</v>
+        <v>6.679208310456385</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.663977352462</v>
+        <v>6.665459648799251</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.664228805423452</v>
+        <v>6.665903030000772</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.669925614461718</v>
+        <v>6.671742274003083</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.687118682327964</v>
+        <v>6.688851549962991</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.693913846332016</v>
+        <v>6.695827280051001</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.705849279864107</v>
+        <v>6.707738518927579</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.710698793159718</v>
+        <v>6.71325740777735</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.697355166846123</v>
+        <v>6.701579026703667</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.6931727889759</v>
+        <v>6.699541563901759</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.714066356183565</v>
+        <v>6.721505946785675</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.749325731183564</v>
+        <v>6.780676069883401</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141389252192583</v>
+        <v>7.141386873709857</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151470646312874</v>
+        <v>7.151466666948888</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154985606419348</v>
+        <v>7.154981681211705</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168328480150986</v>
+        <v>7.16832407717128</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183300144184605</v>
+        <v>7.183295971886376</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19526151539864</v>
+        <v>7.195257632863962</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197560973409812</v>
+        <v>7.197557462915725</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192118401514888</v>
+        <v>7.192115294632737</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175552095159594</v>
+        <v>7.175553842671285</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180489591646186</v>
+        <v>7.180493960382725</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184517792219868</v>
+        <v>7.184521892836705</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189616104232949</v>
+        <v>7.189620156801457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18351659939459</v>
+        <v>7.183523917931441</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182723219948238</v>
+        <v>7.182731773196659</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183749168267408</v>
+        <v>7.183756319936951</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169006068841391</v>
+        <v>7.169012273451106</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155717237055971</v>
+        <v>7.155726469325013</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148579210230821</v>
+        <v>7.14858976236218</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144499826141448</v>
+        <v>7.144513012166097</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124475000886253</v>
+        <v>7.124485760355033</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.112013687712166</v>
+        <v>7.112028348180374</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103502823233319</v>
+        <v>7.103519490323298</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075836198960429</v>
+        <v>7.075854978426201</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051253020587251</v>
+        <v>7.051272286286074</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049644210936082</v>
+        <v>7.04966459691918</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048331150095541</v>
+        <v>7.048356295958319</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055466426058564</v>
+        <v>7.055497257171301</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061423105210627</v>
+        <v>7.06146569818941</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016770933242105</v>
+        <v>7.01680972881063</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969021953420341</v>
+        <v>6.969053721034525</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969607645754055</v>
+        <v>6.969638853666767</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950078939879734</v>
+        <v>6.950119447704446</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.899014120836192</v>
+        <v>6.89903648843908</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862513463892611</v>
+        <v>6.862537002985516</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848079493747436</v>
+        <v>6.848099625508073</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823425929067601</v>
+        <v>6.82341050302241</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841947911338988</v>
+        <v>6.841927749235729</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855460642032906</v>
+        <v>6.855416675850862</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.8873311393295</v>
+        <v>6.887309836088953</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889921264311523</v>
+        <v>6.8899065101774</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877053067605814</v>
+        <v>6.87702759200941</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872543813375225</v>
+        <v>6.872560464299283</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846378421715967</v>
+        <v>6.846388290686294</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842565771513414</v>
+        <v>6.842582248970185</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.8067643805761</v>
+        <v>6.806740426521041</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823995860519325</v>
+        <v>6.823996868808223</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819423197485482</v>
+        <v>6.81943971622914</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814157628631494</v>
+        <v>6.814176564477636</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808249233476311</v>
+        <v>6.808271270208699</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803932163926324</v>
+        <v>6.803956455206582</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802297854593855</v>
+        <v>6.802324380558307</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783904112320983</v>
+        <v>6.783913817552432</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784728453870221</v>
+        <v>6.784746066069277</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775776150007211</v>
+        <v>6.775783780161812</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772316606133668</v>
+        <v>6.77231820036009</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768362670697591</v>
+        <v>6.768365075292307</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762370936918303</v>
+        <v>6.762377870862635</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753120638033783</v>
+        <v>6.753131926271292</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74109498285675</v>
+        <v>6.741111146967736</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729004438927963</v>
+        <v>6.729025109958861</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718834881929146</v>
+        <v>6.718855917652502</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712602333374375</v>
+        <v>6.712622975638538</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.70893797129662</v>
+        <v>6.708966609402657</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707684899611091</v>
+        <v>6.707718910462026</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.699610959813155</v>
+        <v>6.699827705282858</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.689682200171564</v>
+        <v>6.690143835096288</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.679208310456385</v>
+        <v>6.680032212531441</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.665459648799251</v>
+        <v>6.666862022394792</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.665903030000772</v>
+        <v>6.667501375138693</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.671742274003083</v>
+        <v>6.673473349442673</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.688851549962991</v>
+        <v>6.690495165843267</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.695827280051001</v>
+        <v>6.69763169394607</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.707738518927579</v>
+        <v>6.709504931517479</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.71325740777735</v>
+        <v>6.715619364850069</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.701579026703667</v>
+        <v>6.705384561900789</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.699541563901759</v>
+        <v>6.705044750941051</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.721505946785675</v>
+        <v>6.727445012672685</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.780676069883401</v>
+        <v>6.779863209297915</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141386873709857</v>
+        <v>7.141384536232376</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151466666948888</v>
+        <v>7.151462756031355</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154981681211705</v>
+        <v>7.154977823169348</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16832407717128</v>
+        <v>7.168319749470031</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183295971886376</v>
+        <v>7.183291870960061</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195257632863962</v>
+        <v>7.19525381677923</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197557462915725</v>
+        <v>7.197554012509665</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192115294632737</v>
+        <v>7.19211224091779</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175553842671285</v>
+        <v>7.175555558666098</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180493960382725</v>
+        <v>7.180498253437369</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184521892836705</v>
+        <v>7.18452592246593</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189620156801457</v>
+        <v>7.189624139249788</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183523917931441</v>
+        <v>7.183531109891431</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182731773196659</v>
+        <v>7.182740178969433</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183756319936951</v>
+        <v>7.183763348306289</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169012273451106</v>
+        <v>7.169018369956467</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155726469325013</v>
+        <v>7.155735541310757</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14858976236218</v>
+        <v>7.148600131434971</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144513012166097</v>
+        <v>7.144525970670634</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124485760355033</v>
+        <v>7.124496332770153</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.112028348180374</v>
+        <v>7.112042756414498</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103519490323298</v>
+        <v>7.103535872519084</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075854978426201</v>
+        <v>7.07587344010439</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051272286286074</v>
+        <v>7.051291226133629</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.04966459691918</v>
+        <v>7.049684636670754</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048356295958319</v>
+        <v>7.048381011065583</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055497257171301</v>
+        <v>7.055527557968442</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.06146569818941</v>
+        <v>7.061507555998597</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.01680972881063</v>
+        <v>7.016847850487729</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969053721034525</v>
+        <v>6.969084942012112</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969638853666767</v>
+        <v>6.969669529556502</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950119447704446</v>
+        <v>6.950159284704567</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.89903648843908</v>
+        <v>6.899058490012896</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862537002985516</v>
+        <v>6.862560158925248</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848099625508073</v>
+        <v>6.848119439736026</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82341050302241</v>
+        <v>6.823395352882264</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841927749235729</v>
+        <v>6.84190794329694</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855416675850862</v>
+        <v>6.855373454797595</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887309836088953</v>
+        <v>6.887288893226795</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.8899065101774</v>
+        <v>6.889891997081103</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87702759200941</v>
+        <v>6.877002532878921</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872560464299283</v>
+        <v>6.872576834181372</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846388290686294</v>
+        <v>6.84639799801411</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842582248970185</v>
+        <v>6.842598455786131</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806740426521041</v>
+        <v>6.8067168604778</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823996868808223</v>
+        <v>6.823997849010751</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.81943971622914</v>
+        <v>6.819455942793358</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814176564477636</v>
+        <v>6.814195166281561</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808271270208699</v>
+        <v>6.808292923307591</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803956455206582</v>
+        <v>6.803980330485489</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802324380558307</v>
+        <v>6.802350462691917</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783913817552432</v>
+        <v>6.783923356253647</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784746066069277</v>
+        <v>6.784763389053046</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775783780161812</v>
+        <v>6.775791294192593</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.77231820036009</v>
+        <v>6.772319779378304</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768365075292307</v>
+        <v>6.768367437313437</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762377870862635</v>
+        <v>6.762384667182134</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753131926271292</v>
+        <v>6.753142999554529</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741111146967736</v>
+        <v>6.741127013131539</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729025109958861</v>
+        <v>6.729045440747573</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718855917652502</v>
+        <v>6.718876645519194</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712622975638538</v>
+        <v>6.712643340641418</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708966609402657</v>
+        <v>6.708994879883397</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707718910462026</v>
+        <v>6.707752589620037</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.699827705282858</v>
+        <v>6.69999546747673</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.690143835096288</v>
+        <v>6.690528522553016</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.680032212531441</v>
+        <v>6.680743995542965</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.666862022394792</v>
+        <v>6.668077634060067</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.667501375138693</v>
+        <v>6.668848156587851</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.673473349442673</v>
+        <v>6.674897753291717</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.690495165843267</v>
+        <v>6.691773127159463</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.69763169394607</v>
+        <v>6.698986479042397</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.709504931517479</v>
+        <v>6.710726442210056</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.715619364850069</v>
+        <v>6.717176101017692</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.705384561900789</v>
+        <v>6.707975954616613</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.705044750941051</v>
+        <v>6.708645018243816</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.727445012672685</v>
+        <v>6.730517773766235</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.779863209297915</v>
+        <v>6.775469636072118</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141384536232376</v>
+        <v>7.141382238708834</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151462756031355</v>
+        <v>7.151458911809472</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154977823169348</v>
+        <v>7.154974030583201</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168319749470031</v>
+        <v>7.16831549513333</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183291870960061</v>
+        <v>7.183287839590107</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19525381677923</v>
+        <v>7.195250065453191</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197554012509665</v>
+        <v>7.197550620662145</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.19211224091779</v>
+        <v>7.192109239017024</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175555558666098</v>
+        <v>7.175557243987269</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180498253437369</v>
+        <v>7.180502472759615</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.18452592246593</v>
+        <v>7.184529882934872</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189624139249788</v>
+        <v>7.189628053382038</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183531109891431</v>
+        <v>7.183538178529608</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182740178969433</v>
+        <v>7.182748441047126</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183763348306289</v>
+        <v>7.183770256536353</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169018369956467</v>
+        <v>7.169024361157331</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155735541310757</v>
+        <v>7.155744457149588</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148600131434971</v>
+        <v>7.148610322169082</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144525970670634</v>
+        <v>7.14453870749132</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124496332770153</v>
+        <v>7.124506722965236</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.112042756414498</v>
+        <v>7.112056918864452</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103535872519084</v>
+        <v>7.103551977057545</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07587344010439</v>
+        <v>7.075891591987336</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051291226133629</v>
+        <v>7.051309848320404</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049684636670754</v>
+        <v>7.049704338930306</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048381011065583</v>
+        <v>7.048405306384534</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055527557968442</v>
+        <v>7.055557342005064</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061507555998597</v>
+        <v>7.061548697489798</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016847850487729</v>
+        <v>7.016885315664576</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969084942012112</v>
+        <v>6.969115630317566</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969669529556502</v>
+        <v>6.96969968688599</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950159284704567</v>
+        <v>6.950198467369869</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.899058490012896</v>
+        <v>6.899080134441026</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862560158925248</v>
+        <v>6.862582940957076</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848119439736026</v>
+        <v>6.848138943820981</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823395352882264</v>
+        <v>6.82338047133368</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.84190794329694</v>
+        <v>6.841888484191106</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855373454797595</v>
+        <v>6.855330960111428</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887288893226795</v>
+        <v>6.887268301686714</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889891997081103</v>
+        <v>6.889877719189485</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877002532878921</v>
+        <v>6.87697788011652</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872576834181372</v>
+        <v>6.872592930074807</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84639799801411</v>
+        <v>6.84640754763229</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842598455786131</v>
+        <v>6.842614398569191</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.8067168604778</v>
+        <v>6.806693673135431</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823997849010751</v>
+        <v>6.823998802112198</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819455942793358</v>
+        <v>6.819471884843376</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814195166281561</v>
+        <v>6.814213442782064</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808292923307591</v>
+        <v>6.808314202683809</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803980330485489</v>
+        <v>6.804003800339451</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802350462691917</v>
+        <v>6.802376112016997</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783923356253647</v>
+        <v>6.783932732660682</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784763389053046</v>
+        <v>6.784780429859765</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775791294192593</v>
+        <v>6.775798694689295</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772319779378304</v>
+        <v>6.772321343288038</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768367437313437</v>
+        <v>6.768369757902397</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762384667182134</v>
+        <v>6.762391329842668</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753142999554529</v>
+        <v>6.75315386381338</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741127013131539</v>
+        <v>6.741142589301143</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729045440747573</v>
+        <v>6.729065439402068</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718876645519194</v>
+        <v>6.7188970719017</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712643340641418</v>
+        <v>6.712663433458995</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708994879883397</v>
+        <v>6.709022789078583</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707752589620037</v>
+        <v>6.707785939856954</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.69999546747673</v>
+        <v>6.700156540979485</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.690528522553016</v>
+        <v>6.690895096499235</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.680743995542965</v>
+        <v>6.681418075780764</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.668077634060067</v>
+        <v>6.6692314701892</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.668848156587851</v>
+        <v>6.670129933929928</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.674897753291717</v>
+        <v>6.676253879647259</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.691773127159463</v>
+        <v>6.692986158865539</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.698986479042397</v>
+        <v>6.700267411722398</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.710726442210056</v>
+        <v>6.711873776477603</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.717176101017692</v>
+        <v>6.718622678723593</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.707975954616613</v>
+        <v>6.710335802989003</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.708645018243816</v>
+        <v>6.711818075356144</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.730517773766235</v>
+        <v>6.733082064576108</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.775469636072118</v>
+        <v>6.772560955521919</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141382238708834</v>
+        <v>7.141379980123546</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151458911809472</v>
+        <v>7.15145513259165</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154974030583201</v>
+        <v>7.154970301801682</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16831549513333</v>
+        <v>7.168311312311583</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183287839590107</v>
+        <v>7.183283876022003</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195250065453191</v>
+        <v>7.195246377251498</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197550620662145</v>
+        <v>7.197547285895147</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192109239017024</v>
+        <v>7.192106287622936</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175557243987269</v>
+        <v>7.175558899448274</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180502472759615</v>
+        <v>7.180506620232578</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184529882934872</v>
+        <v>7.184533776008679</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189628053382038</v>
+        <v>7.189631900940945</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183538178529608</v>
+        <v>7.183545126990374</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182748441047126</v>
+        <v>7.182756563082214</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183770256536353</v>
+        <v>7.183777047680955</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169024361157331</v>
+        <v>7.169030249757736</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155744457149588</v>
+        <v>7.155753220836841</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148610322169082</v>
+        <v>7.148620339123608</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.14453870749132</v>
+        <v>7.144551228266571</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124506722965236</v>
+        <v>7.124516935608857</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.112056918864452</v>
+        <v>7.11207084176224</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103551977057545</v>
+        <v>7.103567810932704</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075891591987336</v>
+        <v>7.075909441801815</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051309848320404</v>
+        <v>7.051328160764902</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049704338930306</v>
+        <v>7.049723712145878</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048405306384534</v>
+        <v>7.048429192513446</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055557342005064</v>
+        <v>7.055586622378548</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061548697489798</v>
+        <v>7.061589140876189</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016885315664576</v>
+        <v>7.01692214113956</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969115630317566</v>
+        <v>6.969145799444524</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.96969968688599</v>
+        <v>6.969729338668442</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950198467369869</v>
+        <v>6.950237011655327</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.899080134441026</v>
+        <v>6.899101430322668</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862582940957076</v>
+        <v>6.862605358032377</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848138943820981</v>
+        <v>6.84815814492739</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82338047133368</v>
+        <v>6.823365851318648</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841888484191106</v>
+        <v>6.841869362909113</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855330960111428</v>
+        <v>6.85528917365458</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887268301686714</v>
+        <v>6.887248052712928</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889877719189485</v>
+        <v>6.889863670855207</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87697788011652</v>
+        <v>6.876953623947115</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872592930074807</v>
+        <v>6.872608758798917</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84640754763229</v>
+        <v>6.846416943347352</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842614398569191</v>
+        <v>6.842630083714099</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806693673135431</v>
+        <v>6.806670855477107</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823998802112198</v>
+        <v>6.823999729055789</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819471884843376</v>
+        <v>6.819487549779233</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814213442782064</v>
+        <v>6.814231402416504</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808314202683809</v>
+        <v>6.808335117910378</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.804003800339451</v>
+        <v>6.804026874990003</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802376112016997</v>
+        <v>6.802401339194717</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783932732660682</v>
+        <v>6.783941950867589</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784780429859765</v>
+        <v>6.784797195302101</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775798694689295</v>
+        <v>6.77580598416671</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772321343288038</v>
+        <v>6.772322892194635</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768369757902397</v>
+        <v>6.768372038159568</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762391329842668</v>
+        <v>6.762397862661908</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.75315386381338</v>
+        <v>6.753164524766082</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741142589301143</v>
+        <v>6.741157883155178</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729065439402068</v>
+        <v>6.729085113782205</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.7188970719017</v>
+        <v>6.718917203010134</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712663433458995</v>
+        <v>6.712683259062205</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709022789078583</v>
+        <v>6.709050343209463</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707785939856954</v>
+        <v>6.707818964015035</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.700156540979485</v>
+        <v>6.700170669910117</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.690895096499235</v>
+        <v>6.691168195999518</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.681418075780764</v>
+        <v>6.681939073735961</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.6692314701892</v>
+        <v>6.670123039823924</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.670129933929928</v>
+        <v>6.671668926440402</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.676253879647259</v>
+        <v>6.678013413389369</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.692986158865539</v>
+        <v>6.694885475958346</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.700267411722398</v>
+        <v>6.702573737537729</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.711873776477603</v>
+        <v>6.714479213120657</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.718622678723593</v>
+        <v>6.721769715371442</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.710335802989003</v>
+        <v>6.716175702867048</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.711818075356144</v>
+        <v>6.720063913593044</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.733082064576108</v>
+        <v>6.743469688534189</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,15 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.772560955521919</v>
+        <v>6.786655725789367</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
+        <v>46395</v>
+      </c>
+      <c r="B120">
+        <v>6.819923850789366</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.681939073735961</v>
+        <v>6.681935521532534</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.670123039823924</v>
+        <v>6.670112527467729</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.671668926440402</v>
+        <v>6.671510320731926</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.678013413389369</v>
+        <v>6.677904823398467</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.694885475958346</v>
+        <v>6.694800984376973</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.702573737537729</v>
+        <v>6.702505837717883</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.714479213120657</v>
+        <v>6.714422329054698</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.721769715371442</v>
+        <v>6.721719311433266</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.716175702867048</v>
+        <v>6.716116541216231</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.720063913593044</v>
+        <v>6.720000127266154</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.743469688534189</v>
+        <v>6.74339429007653</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.786655725789367</v>
+        <v>6.786533522773738</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.819923850789366</v>
+        <v>6.819801647773738</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141379980123546</v>
+        <v>7.141377759494972</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.15145513259165</v>
+        <v>7.151451416743005</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154970301801682</v>
+        <v>7.154966635228295</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168311312311583</v>
+        <v>7.16830719921685</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183283876022003</v>
+        <v>7.183279978559755</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195246377251498</v>
+        <v>7.195242750594334</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197547285895147</v>
+        <v>7.197544006779972</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192106287622936</v>
+        <v>7.192103385471643</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175558899448274</v>
+        <v>7.175560525834132</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180506620232578</v>
+        <v>7.180510697675798</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184533776008679</v>
+        <v>7.184537603392945</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189631900940945</v>
+        <v>7.189635683610479</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183545126990374</v>
+        <v>7.18355195831216</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182756563082214</v>
+        <v>7.182764548604453</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183777047680955</v>
+        <v>7.183783724691289</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169030249757736</v>
+        <v>7.169036038369955</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155753220836841</v>
+        <v>7.155761836232745</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148620339123608</v>
+        <v>7.148630186703643</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144551228266571</v>
+        <v>7.144563538445251</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124516935608857</v>
+        <v>7.124526975211531</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11207084176224</v>
+        <v>7.112084531131072</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103567810932704</v>
+        <v>7.103583380905822</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075909441801815</v>
+        <v>7.075926997019967</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051328160764902</v>
+        <v>7.05134617112484</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049723712145878</v>
+        <v>7.049742764486107</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048429192513446</v>
+        <v>7.048452679697033</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055586622378548</v>
+        <v>7.055615411747723</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061589140876189</v>
+        <v>7.061628903759304</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.01692214113956</v>
+        <v>7.016958343143319</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969145799444524</v>
+        <v>6.969175462435453</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969729338668442</v>
+        <v>6.969758497486111</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950237011655327</v>
+        <v>6.950274933002567</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.899101430322668</v>
+        <v>6.899122385984082</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862605358032377</v>
+        <v>6.862627418820178</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84815814492739</v>
+        <v>6.84817705000287</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823365851318648</v>
+        <v>6.823351486023629</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841869362909113</v>
+        <v>6.841850570750492</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.85528917365458</v>
+        <v>6.855248077887492</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887248052712928</v>
+        <v>6.88722813783785</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889863670855207</v>
+        <v>6.889849846609444</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.876953623947115</v>
+        <v>6.876929754905596</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872608758798917</v>
+        <v>6.872624326948666</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846416943347352</v>
+        <v>6.846426188844474</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842630083714099</v>
+        <v>6.842645517410903</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806670855477107</v>
+        <v>6.806648398768669</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823999729055789</v>
+        <v>6.824000630744795</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819487549779233</v>
+        <v>6.819502944747125</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814231402416504</v>
+        <v>6.814249053333658</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808335117910378</v>
+        <v>6.808355678236784</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.804026874990003</v>
+        <v>6.804049564318552</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802401339194717</v>
+        <v>6.802426154539734</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783941950867589</v>
+        <v>6.783951014832288</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784797195302101</v>
+        <v>6.784813691976062</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.77580598416671</v>
+        <v>6.77581316506731</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772322892194635</v>
+        <v>6.772324426208471</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768372038159568</v>
+        <v>6.768374279146157</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762397862661908</v>
+        <v>6.762404269316076</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753164524766082</v>
+        <v>6.753174987928406</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741157883155178</v>
+        <v>6.741172902109424</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729085113782205</v>
+        <v>6.729104471508832</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718917203010134</v>
+        <v>6.718937044896794</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712683259062205</v>
+        <v>6.712702822318705</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709050343209463</v>
+        <v>6.70907754838017</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707818964015035</v>
+        <v>6.707851664998413</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.700170669910117</v>
+        <v>6.700184790554855</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.691168195999518</v>
+        <v>6.691475332876507</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.681935521532534</v>
+        <v>6.682483930562216</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.670112527467729</v>
+        <v>6.671010636288786</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.671510320731926</v>
+        <v>6.672865532402899</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.677904823398467</v>
+        <v>6.679513734888298</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.694800984376973</v>
+        <v>6.696542195204339</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.702505837717883</v>
+        <v>6.70461677372476</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.714422329054698</v>
+        <v>6.716778627722828</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.721719311433266</v>
+        <v>6.724518183215372</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.716116541216231</v>
+        <v>6.721190792698276</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.720000127266154</v>
+        <v>6.726928564092415</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.74339429007653</v>
+        <v>6.751610525855017</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.786533522773738</v>
+        <v>6.795793924731441</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.819801647773738</v>
+        <v>6.82906204973144</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141377759494972</v>
+        <v>7.1413991985401</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151451416743005</v>
+        <v>7.151487285471848</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154966635228295</v>
+        <v>7.155002015241526</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16830719921685</v>
+        <v>7.168346885546281</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183279978559755</v>
+        <v>7.183317585698733</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195242750594334</v>
+        <v>7.19527774599707</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197544006779972</v>
+        <v>7.197575648787394</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192103385471643</v>
+        <v>7.192131389484038</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175560525834132</v>
+        <v>7.175544771958844</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180510697675798</v>
+        <v>7.180471318398234</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184537603392945</v>
+        <v>7.184500640994838</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189635683610479</v>
+        <v>7.18959915437105</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18355195831216</v>
+        <v>7.18348599022284</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182764548604453</v>
+        <v>7.182687451777737</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183783724691289</v>
+        <v>7.183719261347242</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169036038369955</v>
+        <v>7.168980109761543</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155761836232745</v>
+        <v>7.155678617120882</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148630186703643</v>
+        <v>7.148535070683304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144563538445251</v>
+        <v>7.144444682688154</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124526975211531</v>
+        <v>7.124429989602453</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.112084531131072</v>
+        <v>7.111952386320898</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103583380905822</v>
+        <v>7.103433152083165</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075926997019967</v>
+        <v>7.075757733418914</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.05134617112484</v>
+        <v>7.051172525273978</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049742764486107</v>
+        <v>7.049559018969134</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048452679697033</v>
+        <v>7.048226025901912</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055615411747723</v>
+        <v>7.055337510171514</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061628903759304</v>
+        <v>7.061244980600948</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016958343143319</v>
+        <v>7.016608641966902</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969175462435453</v>
+        <v>6.968889119640489</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969758497486111</v>
+        <v>6.969477207762373</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950274933002567</v>
+        <v>6.949909850526915</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.899122385984082</v>
+        <v>6.898920801843229</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862627418820178</v>
+        <v>6.862415280103021</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84817705000287</v>
+        <v>6.847995635196098</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823351486023629</v>
+        <v>6.823490548180395</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841850570750492</v>
+        <v>6.842032320147014</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855248077887492</v>
+        <v>6.855644356672904</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.88722813783785</v>
+        <v>6.887420148467378</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889849846609444</v>
+        <v>6.889982814832212</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.876929754905596</v>
+        <v>6.877159348670736</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872624326948666</v>
+        <v>6.87247424942163</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846426188844474</v>
+        <v>6.846337246026196</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842645517410903</v>
+        <v>6.842497015142671</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806648398768669</v>
+        <v>6.806864274117725</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.824000630744795</v>
+        <v>6.823991525191849</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819502944747125</v>
+        <v>6.819354037441593</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814249053333658</v>
+        <v>6.814078358718962</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808355678236784</v>
+        <v>6.808157039309828</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.804049564318552</v>
+        <v>6.803830613951565</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802426154539734</v>
+        <v>6.802187078457318</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783951014832288</v>
+        <v>6.783863536045706</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784813691976062</v>
+        <v>6.784654963723272</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.77581316506731</v>
+        <v>6.775744413576108</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772324426208471</v>
+        <v>6.772092677556798</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768374279146157</v>
+        <v>6.767993123750012</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762404269316076</v>
+        <v>6.762764669800127</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753174987928406</v>
+        <v>6.755213853586223</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741172902109424</v>
+        <v>6.743261641090569</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729104471508832</v>
+        <v>6.732459786916685</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718937044896794</v>
+        <v>6.726198172465413</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712702822318705</v>
+        <v>6.722031915650353</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.70907754838017</v>
+        <v>6.720501076260343</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707851664998413</v>
+        <v>6.719814934853497</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.700184790554855</v>
+        <v>6.710754269813979</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.691475332876507</v>
+        <v>6.698688088975024</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.682483930562216</v>
+        <v>6.687716961459119</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.671010636288786</v>
+        <v>6.673551542963038</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.672865532402899</v>
+        <v>6.676376374280288</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.679513734888298</v>
+        <v>6.683850270270759</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.696542195204339</v>
+        <v>6.690005348728528</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.70461677372476</v>
+        <v>6.695578170614024</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.716778627722828</v>
+        <v>6.700868991216129</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.724518183215372</v>
+        <v>6.696828783308575</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.721190792698276</v>
+        <v>6.705957622574525</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.726928564092415</v>
+        <v>6.712736472614308</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.751610525855017</v>
+        <v>6.770219404948202</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.795793924731441</v>
+        <v>6.817528303543783</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.82906204973144</v>
+        <v>6.86339125650947</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.1413991985401</v>
+        <v>7.141373428344012</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151487285471848</v>
+        <v>7.151444168883336</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155002015241526</v>
+        <v>7.154959482581869</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168346885546281</v>
+        <v>7.168299175349725</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183317585698733</v>
+        <v>7.183272375446984</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19527774599707</v>
+        <v>7.195235675853556</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197575648787394</v>
+        <v>7.197537610024751</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192131389484038</v>
+        <v>7.192097724049274</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175544771958844</v>
+        <v>7.175563694385499</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180471318398234</v>
+        <v>7.180518649449102</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184500640994838</v>
+        <v>7.184545067632265</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18959915437105</v>
+        <v>7.18964306073806</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18348599022284</v>
+        <v>7.183565281188922</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182687451777737</v>
+        <v>7.182780123646268</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183719261347242</v>
+        <v>7.183796747626332</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168980109761543</v>
+        <v>7.169047325643072</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155678617120882</v>
+        <v>7.155778636949642</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148535070683304</v>
+        <v>7.148649390628949</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144444682688154</v>
+        <v>7.144587547907652</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124429989602453</v>
+        <v>7.124546552585247</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111952386320898</v>
+        <v>7.112111232382301</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103433152083165</v>
+        <v>7.103613755084268</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075757733418914</v>
+        <v>7.075961252344541</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051172525273978</v>
+        <v>7.051381314981272</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049559018969134</v>
+        <v>7.049779937886098</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048226025901912</v>
+        <v>7.04849849652625</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055337510171514</v>
+        <v>7.055671566023908</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061244980600948</v>
+        <v>7.0617064555149</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016608641966902</v>
+        <v>7.017028938962318</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968889119640489</v>
+        <v>6.969233320034276</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969477207762373</v>
+        <v>6.969815384506452</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949909850526915</v>
+        <v>6.950348966203787</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898920801843229</v>
+        <v>6.899163308650252</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862415280103021</v>
+        <v>6.862670504863086</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847995635196098</v>
+        <v>6.848213998815293</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823490548180395</v>
+        <v>6.823323493499458</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842032320147014</v>
+        <v>6.841813940466836</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855644356672904</v>
+        <v>6.855167891110023</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887420148467378</v>
+        <v>6.887189277884505</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889982814832212</v>
+        <v>6.889822849359232</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877159348670736</v>
+        <v>6.876883141823424</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.87247424942163</v>
+        <v>6.872654706837545</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846337246026196</v>
+        <v>6.846444243347475</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842497015142671</v>
+        <v>6.842675654245316</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806864274117725</v>
+        <v>6.806604534613005</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823991525191849</v>
+        <v>6.824002361784267</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819354037441593</v>
+        <v>6.819532952158607</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814078358718962</v>
+        <v>6.814283460240927</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808157039309828</v>
+        <v>6.808395769649778</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803830613951565</v>
+        <v>6.804093824917895</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802187078457318</v>
+        <v>6.802474589340656</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783863536045706</v>
+        <v>6.783968695219428</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784654963723272</v>
+        <v>6.784845904370281</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775744413576108</v>
+        <v>6.775827210561321</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772092677556798</v>
+        <v>6.772327450021405</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767993123750012</v>
+        <v>6.768378647366881</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762764669800127</v>
+        <v>6.762416718164875</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.755213853586223</v>
+        <v>6.753195341984617</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743261641090569</v>
+        <v>6.741202143732481</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.732459786916685</v>
+        <v>6.729142266341814</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.726198172465413</v>
+        <v>6.718975884451387</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.722031915650353</v>
+        <v>6.712741180756671</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.720501076260343</v>
+        <v>6.709130935680914</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.719814934853497</v>
+        <v>6.707916109320247</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.710754269813979</v>
+        <v>6.700212989326332</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.698688088975024</v>
+        <v>6.69149804381028</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.687716961459119</v>
+        <v>6.682839034956435</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.673551542963038</v>
+        <v>6.671891274751569</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.676376374280288</v>
+        <v>6.674354744519627</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.683850270270759</v>
+        <v>6.681410214231542</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.690005348728528</v>
+        <v>6.698509384031389</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.695578170614024</v>
+        <v>6.707048734493601</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.700868991216129</v>
+        <v>6.719373606473842</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.696828783308575</v>
+        <v>6.727528639203499</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.705957622574525</v>
+        <v>6.727399172302873</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.712736472614308</v>
+        <v>6.735192632640928</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.770219404948202</v>
+        <v>6.760217734152486</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.817528303543783</v>
+        <v>6.801256266758846</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.86339125650947</v>
+        <v>6.844442669545125</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141373428344012</v>
+        <v>7.141396644753593</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151444168883336</v>
+        <v>7.151483013535501</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154959482581869</v>
+        <v>7.154997803041017</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168299175349725</v>
+        <v>7.168342160925167</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183272375446984</v>
+        <v>7.183313108439411</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195235675853556</v>
+        <v>7.19527357952178</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197537610024751</v>
+        <v>7.197571881535373</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192097724049274</v>
+        <v>7.192128055420272</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175563694385499</v>
+        <v>7.175546654615192</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180518649449102</v>
+        <v>7.180476010791521</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184545067632265</v>
+        <v>7.184505045178753</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18964306073806</v>
+        <v>7.189603506786826</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183565281188922</v>
+        <v>7.18349385000786</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182780123646268</v>
+        <v>7.182696635500971</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183796747626332</v>
+        <v>7.183726940140343</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169047325643072</v>
+        <v>7.168986776858595</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155778636949642</v>
+        <v>7.155688534935102</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148649390628949</v>
+        <v>7.148546405721901</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144587547907652</v>
+        <v>7.144458841429304</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124546552585247</v>
+        <v>7.124441549188859</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.112111232382301</v>
+        <v>7.111968124929918</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103613755084268</v>
+        <v>7.103451036359605</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075961252344541</v>
+        <v>7.07577786968504</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051381314981272</v>
+        <v>7.051193182147256</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049779937886098</v>
+        <v>7.049580883560079</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.04849849652625</v>
+        <v>7.048253012422216</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055671566023908</v>
+        <v>7.055370607979723</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.0617064555149</v>
+        <v>7.061290716561622</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.017028938962318</v>
+        <v>7.016650319821171</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969233320034276</v>
+        <v>6.968923223609309</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969815384506452</v>
+        <v>6.969510688090438</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950348966203787</v>
+        <v>6.949953218056995</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.899163308650252</v>
+        <v>6.898944728504942</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862670504863086</v>
+        <v>6.862440450575479</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848213998815293</v>
+        <v>6.848017115806103</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823323493499458</v>
+        <v>6.82347393984949</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841813940466836</v>
+        <v>6.8420106330974</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855167891110023</v>
+        <v>6.855597208904624</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887189277884505</v>
+        <v>6.887397306670249</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889822849359232</v>
+        <v>6.889967034222956</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.876883141823424</v>
+        <v>6.87713209929535</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872654706837545</v>
+        <v>6.872492100092003</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846444243347475</v>
+        <v>6.846347803612996</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842675654245316</v>
+        <v>6.842514645829392</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806604534613005</v>
+        <v>6.806838668590106</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.824002361784267</v>
+        <v>6.823992656602249</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819532952158607</v>
+        <v>6.819371807291825</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814283460240927</v>
+        <v>6.814098724640587</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808395769649778</v>
+        <v>6.808180716982443</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.804093824917895</v>
+        <v>6.803856682658918</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802474589340656</v>
+        <v>6.802215497746506</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783968695219428</v>
+        <v>6.783873952822336</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784845904370281</v>
+        <v>6.784673808015268</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775827210561321</v>
+        <v>6.775752535720577</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772327450021405</v>
+        <v>6.772094929202353</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768378647366881</v>
+        <v>6.767996125374474</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762416718164875</v>
+        <v>6.762770606353794</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753195341984617</v>
+        <v>6.75522188274963</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741202143732481</v>
+        <v>6.743274548738975</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729142266341814</v>
+        <v>6.732478579650801</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718975884451387</v>
+        <v>6.726218449426719</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712741180756671</v>
+        <v>6.722055948753175</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709130935680914</v>
+        <v>6.720540310600947</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707916109320247</v>
+        <v>6.719876699816098</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.700212989326332</v>
+        <v>6.710807634214465</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.69149804381028</v>
+        <v>6.698614718451087</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.682839034956435</v>
+        <v>6.68788177188704</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.671891274751569</v>
+        <v>6.674235904395506</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.674354744519627</v>
+        <v>6.677308758555849</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.681410214231542</v>
+        <v>6.685041907966793</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.698509384031389</v>
+        <v>6.691586217477786</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.707048734493601</v>
+        <v>6.697597561521444</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.719373606473842</v>
+        <v>6.703352427040221</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.727528639203499</v>
+        <v>6.700171906175822</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.727399172302873</v>
+        <v>6.710909234635057</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.735192632640928</v>
+        <v>6.718945249315654</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.760217734152486</v>
+        <v>6.774880116924994</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.801256266758846</v>
+        <v>6.82059522382476</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.844442669545125</v>
+        <v>6.862309036155824</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141396644753593</v>
+        <v>7.14137131601677</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151483013535501</v>
+        <v>7.151440633865536</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154997803041017</v>
+        <v>7.154955993571356</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168342160925167</v>
+        <v>7.168295261287373</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183313108439411</v>
+        <v>7.183268666675828</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19527357952178</v>
+        <v>7.195232224863206</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197571881535373</v>
+        <v>7.197534489756038</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192128055420272</v>
+        <v>7.192094962452737</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175546654615192</v>
+        <v>7.175565237989518</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180476010791521</v>
+        <v>7.180522527123664</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184505045178753</v>
+        <v>7.184548707622532</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189603506786826</v>
+        <v>7.189646658291698</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18349385000786</v>
+        <v>7.183571778329606</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182696635500971</v>
+        <v>7.182787719656522</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183726940140343</v>
+        <v>7.183803098977781</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168986776858595</v>
+        <v>7.169052829103475</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155688534935102</v>
+        <v>7.155786829365161</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148546405721901</v>
+        <v>7.148658755070814</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144458841429304</v>
+        <v>7.14459925721053</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124441549188859</v>
+        <v>7.124556098645048</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111968124929918</v>
+        <v>7.112124255343031</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103451036359605</v>
+        <v>7.103628571732354</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07577786968504</v>
+        <v>7.075977966213132</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051193182147256</v>
+        <v>7.051398462582448</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049580883560079</v>
+        <v>7.049798073986324</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048253012422216</v>
+        <v>7.04852084502148</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055370607979723</v>
+        <v>7.055698954215062</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061290716561622</v>
+        <v>7.061744276754892</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016650319821171</v>
+        <v>7.017063362608081</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968923223609309</v>
+        <v>6.969261538634695</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969510688090438</v>
+        <v>6.96984313587354</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949953218056995</v>
+        <v>6.950385106553389</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898944728504942</v>
+        <v>6.899183291036673</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862440450575479</v>
+        <v>6.86269154614095</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848017115806103</v>
+        <v>6.848232055434007</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82347393984949</v>
+        <v>6.823309853773939</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.8420106330974</v>
+        <v>6.841796086369594</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855597208904624</v>
+        <v>6.855128767797563</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887397306670249</v>
+        <v>6.887170317209115</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889967034222956</v>
+        <v>6.889809666248607</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87713209929535</v>
+        <v>6.876860380295966</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872492100092003</v>
+        <v>6.872669530724917</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846347803612996</v>
+        <v>6.846453059159037</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842514645829392</v>
+        <v>6.842690368810775</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806838668590106</v>
+        <v>6.806583111014847</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823992656602249</v>
+        <v>6.824003192758923</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819371807291825</v>
+        <v>6.819547577719584</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814098724640587</v>
+        <v>6.814300231192512</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808180716982443</v>
+        <v>6.808415317736026</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803856682658918</v>
+        <v>6.804115414373481</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802215497746506</v>
+        <v>6.80249822781542</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783873952822336</v>
+        <v>6.783977318926093</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784673808015268</v>
+        <v>6.784861632273888</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775752535720577</v>
+        <v>6.775834079700212</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772094929202353</v>
+        <v>6.772328940061837</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767996125374474</v>
+        <v>6.768380776542782</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762770606353794</v>
+        <v>6.762422767060592</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.75522188274963</v>
+        <v>6.753205242974085</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743274548738975</v>
+        <v>6.74121638001435</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.732478579650801</v>
+        <v>6.729160717571461</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.726218449426719</v>
+        <v>6.718994893474175</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.722055948753175</v>
+        <v>6.712759985173396</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.720540310600947</v>
+        <v>6.709157129447204</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.719876699816098</v>
+        <v>6.70794785870824</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.710807634214465</v>
+        <v>6.700227059277447</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.698614718451087</v>
+        <v>6.691551596443678</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.68788177188704</v>
+        <v>6.683062069963261</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.674235904395506</v>
+        <v>6.672389241393757</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.677308758555849</v>
+        <v>6.67524760065535</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.685041907966793</v>
+        <v>6.682494033981424</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.691586217477786</v>
+        <v>6.699675386568286</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.697597561521444</v>
+        <v>6.708473715329347</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.703352427040221</v>
+        <v>6.720905390903541</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.700171906175822</v>
+        <v>6.729273388974713</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.710909234635057</v>
+        <v>6.730651730564661</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.718945249315654</v>
+        <v>6.739317584146786</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.774880116924994</v>
+        <v>6.764405046701562</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.82059522382476</v>
+        <v>6.80409235050454</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.862309036155824</v>
+        <v>6.841672662704932</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.683062069963261</v>
+        <v>6.683060737536316</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.672389241393757</v>
+        <v>6.672388163970506</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.67524760065535</v>
+        <v>6.675175427419857</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.682494033981424</v>
+        <v>6.682491986682659</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.699675386568286</v>
+        <v>6.699672721150328</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.708473715329347</v>
+        <v>6.70847034466577</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.720905390903541</v>
+        <v>6.720901233668904</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.729273388974713</v>
+        <v>6.729268270107561</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.730651730564661</v>
+        <v>6.730643444415589</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.739317584146786</v>
+        <v>6.73930657027614</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.764405046701562</v>
+        <v>6.764390173503667</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.80409235050454</v>
+        <v>6.804069176881106</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.841672662704932</v>
+        <v>6.841623058936646</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.14137131601677</v>
+        <v>7.141394136566749</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151440633865536</v>
+        <v>7.151478817695259</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154955993571356</v>
+        <v>7.15499366546951</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168295261287373</v>
+        <v>7.168337519940132</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183268666675828</v>
+        <v>7.183308710480521</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195232224863206</v>
+        <v>7.195269486882465</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197534489756038</v>
+        <v>7.197568181051015</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192094962452737</v>
+        <v>7.192124780432577</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175565237989518</v>
+        <v>7.175548502055543</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180522527123664</v>
+        <v>7.180480618979706</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184548707622532</v>
+        <v>7.184509370386467</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189646658291698</v>
+        <v>7.189607781195747</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183571778329606</v>
+        <v>7.183501568987202</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182787719656522</v>
+        <v>7.182705655227442</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183803098977781</v>
+        <v>7.183734481819771</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169052829103475</v>
+        <v>7.168993323604411</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155786829365161</v>
+        <v>7.155698274379152</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148658755070814</v>
+        <v>7.148557537065669</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.14459925721053</v>
+        <v>7.144472747144517</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124556098645048</v>
+        <v>7.124452900583495</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.112124255343031</v>
+        <v>7.111983583126143</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103628571732354</v>
+        <v>7.103468604144709</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075977966213132</v>
+        <v>7.075797653299366</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051398462582448</v>
+        <v>7.051213477442776</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049798073986324</v>
+        <v>7.049602363783358</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.04852084502148</v>
+        <v>7.048279520292018</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055698954215062</v>
+        <v>7.055403116255498</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061744276754892</v>
+        <v>7.061335634975069</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.017063362608081</v>
+        <v>7.016691247742672</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969261538634695</v>
+        <v>6.968956719945068</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.96984313587354</v>
+        <v>6.969543577642926</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950385106553389</v>
+        <v>6.949995842987089</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.899183291036673</v>
+        <v>6.898968250517486</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.86269154614095</v>
+        <v>6.86246519772356</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848232055434007</v>
+        <v>6.848038246889896</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823309853773939</v>
+        <v>6.823457639474965</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841796086369594</v>
+        <v>6.841989343064949</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855128767797563</v>
+        <v>6.85555088811315</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887170317209115</v>
+        <v>6.887374864752328</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889809666248607</v>
+        <v>6.889951520001205</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.876860380295966</v>
+        <v>6.877105310282253</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872669530724917</v>
+        <v>6.872509638956745</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846453059159037</v>
+        <v>6.846358182452521</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842690368810775</v>
+        <v>6.842531977125413</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806583111014847</v>
+        <v>6.806813491508793</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.824003192758923</v>
+        <v>6.823993755517277</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819547577719584</v>
+        <v>6.819389251400514</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814300231192512</v>
+        <v>6.814118718268183</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808415317736026</v>
+        <v>6.808203967688012</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.804115414373481</v>
+        <v>6.803882289187915</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.80249822781542</v>
+        <v>6.802243425184351</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783977318926093</v>
+        <v>6.783884184575678</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784861632273888</v>
+        <v>6.784692332488733</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775834079700212</v>
+        <v>6.775760530576305</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772328940061837</v>
+        <v>6.772097154888469</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768380776542782</v>
+        <v>6.767999072291994</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762422767060592</v>
+        <v>6.762776417326829</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753205242974085</v>
+        <v>6.75522974145907</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74121638001435</v>
+        <v>6.743287196089959</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729160717571461</v>
+        <v>6.732497033305487</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718994893474175</v>
+        <v>6.726238380797839</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712759985173396</v>
+        <v>6.722079576449638</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709157129447204</v>
+        <v>6.720578901748071</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.70794785870824</v>
+        <v>6.719937563602719</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.700227059277447</v>
+        <v>6.71086027389503</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.691551596443678</v>
+        <v>6.698657711651531</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.683060737536316</v>
+        <v>6.688007348608732</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.672388163970506</v>
+        <v>6.674679350140929</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.675175427419857</v>
+        <v>6.677833511326956</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.682491986682659</v>
+        <v>6.685966809934635</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.699672721150328</v>
+        <v>6.692797768842055</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.70847034466577</v>
+        <v>6.699280118682296</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.720901233668904</v>
+        <v>6.705440260322208</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.729268270107561</v>
+        <v>6.703020323597776</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.730643444415589</v>
+        <v>6.7140409765924</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.73930657027614</v>
+        <v>6.723837817681586</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.764390173503667</v>
+        <v>6.777617762943819</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.804069176881106</v>
+        <v>6.820318065006164</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,15 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.841623058936646</v>
+        <v>6.854945181466407</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>6.822785452546427</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141394136566749</v>
+        <v>7.141369238034023</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151478817695259</v>
+        <v>7.151437156199199</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15499366546951</v>
+        <v>7.154952560890028</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168337519940132</v>
+        <v>7.168291410367621</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183308710480521</v>
+        <v>7.183265017764993</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195269486882465</v>
+        <v>7.195228829599941</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197568181051015</v>
+        <v>7.197531419878217</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192124780432577</v>
+        <v>7.192092245444892</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175548502055543</v>
+        <v>7.175566755397566</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180480618979706</v>
+        <v>7.180526341462128</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184509370386467</v>
+        <v>7.184552288198071</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189607781195747</v>
+        <v>7.189650197151469</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183501568987202</v>
+        <v>7.18357816951052</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182705655227442</v>
+        <v>7.182795192144305</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183734481819771</v>
+        <v>7.183809347055986</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168993323604411</v>
+        <v>7.169058242181503</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155698274379152</v>
+        <v>7.155794887688365</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148557537065669</v>
+        <v>7.148667966342735</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144472747144517</v>
+        <v>7.144610775969073</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124452900583495</v>
+        <v>7.124565488253102</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111983583126143</v>
+        <v>7.11213706694676</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103468604144709</v>
+        <v>7.103643149380851</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075797653299366</v>
+        <v>7.075994413028107</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051213477442776</v>
+        <v>7.05141533632724</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049602363783358</v>
+        <v>7.049815919312359</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048279520292018</v>
+        <v>7.048542832296375</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055403116255498</v>
+        <v>7.055725898002281</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061335634975069</v>
+        <v>7.061781482271487</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016691247742672</v>
+        <v>7.017097222485543</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968956719945068</v>
+        <v>6.969289299117083</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969543577642926</v>
+        <v>6.969870440635892</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.949995842987089</v>
+        <v>6.950420680992261</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898968250517486</v>
+        <v>6.899202963985227</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.86246519772356</v>
+        <v>6.862712263196384</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848038246889896</v>
+        <v>6.84824984179974</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823457639474965</v>
+        <v>6.823296443757293</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841989343064949</v>
+        <v>6.841778529428291</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.85555088811315</v>
+        <v>6.855090270527516</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887374864752328</v>
+        <v>6.88715165941742</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889951520001205</v>
+        <v>6.889796687001756</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877105310282253</v>
+        <v>6.876837970901201</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872509638956745</v>
+        <v>6.872684118350582</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846358182452521</v>
+        <v>6.846461738372524</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842531977125413</v>
+        <v>6.842704854798233</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806813491508793</v>
+        <v>6.806562016045238</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823993755517277</v>
+        <v>6.824004001730831</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819389251400514</v>
+        <v>6.819561959566317</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814118718268183</v>
+        <v>6.814316723371233</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808203967688012</v>
+        <v>6.808434544945268</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803882289187915</v>
+        <v>6.804136654901373</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802243425184351</v>
+        <v>6.802521492519871</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783884184575678</v>
+        <v>6.783985802968866</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784692332488733</v>
+        <v>6.784877115790943</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775760530576305</v>
+        <v>6.775840849357794</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772097154888469</v>
+        <v>6.772330415691307</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767999072291994</v>
+        <v>6.768382870334678</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762776417326829</v>
+        <v>6.762428703204577</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.75522974145907</v>
+        <v>6.753214966379685</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743287196089959</v>
+        <v>6.741230368641877</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.732497033305487</v>
+        <v>6.72917888040987</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.726238380797839</v>
+        <v>6.719013635993196</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.722079576449638</v>
+        <v>6.712778545717618</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.720578901748071</v>
+        <v>6.709182997529084</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.719937563602719</v>
+        <v>6.70797929700761</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.71086027389503</v>
+        <v>6.700241104563402</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.698657711651531</v>
+        <v>6.691544936615851</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.688007348608732</v>
+        <v>6.683225542285156</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.674679350140929</v>
+        <v>6.672747416287004</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.677833511326956</v>
+        <v>6.675498793209854</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.685966809934635</v>
+        <v>6.682903662721417</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.692797768842055</v>
+        <v>6.69993902912862</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.699280118682296</v>
+        <v>6.708788851211697</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.705440260322208</v>
+        <v>6.72108962751401</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.703020323597776</v>
+        <v>6.729350573281787</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.7140409765924</v>
+        <v>6.730844212719182</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.723837817681586</v>
+        <v>6.739902441993647</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.777617762943819</v>
+        <v>6.763966840103109</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.820318065006164</v>
+        <v>6.800368035713142</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.854945181466407</v>
+        <v>6.828540139863575</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>6.822785452546427</v>
+        <v>6.795272014863576</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141369238034023</v>
+        <v>7.141391672769084</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151437156199199</v>
+        <v>7.151474695935936</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154952560890028</v>
+        <v>7.154989600561365</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168291410367621</v>
+        <v>7.168332960390211</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183265017764993</v>
+        <v>7.18330438973404</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195228829599941</v>
+        <v>7.195265466133912</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197531419878217</v>
+        <v>7.197564545575138</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192092245444892</v>
+        <v>7.192121562964781</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175566755397566</v>
+        <v>7.175550315256659</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180526341462128</v>
+        <v>7.180485145208934</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184552288198071</v>
+        <v>7.184513618723161</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189650197151469</v>
+        <v>7.189611979676086</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18357816951052</v>
+        <v>7.183509150910281</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182795192144305</v>
+        <v>7.182714515309844</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183809347055986</v>
+        <v>7.183741890024886</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169058242181503</v>
+        <v>7.168999753227354</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155794887688365</v>
+        <v>7.155707840219907</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148667966342735</v>
+        <v>7.14856847015308</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144610775969073</v>
+        <v>7.144486406553819</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124565488253102</v>
+        <v>7.124464049357795</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11213706694676</v>
+        <v>7.111998768332443</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103643149380851</v>
+        <v>7.103485863758793</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075994413028107</v>
+        <v>7.075817093437674</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.05141533632724</v>
+        <v>7.051233420562937</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049815919312359</v>
+        <v>7.049623469677833</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048542832296375</v>
+        <v>7.048305562124934</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055725898002281</v>
+        <v>7.055435050597297</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061781482271487</v>
+        <v>7.061379757544024</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.017097222485543</v>
+        <v>7.016731445771855</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969289299117083</v>
+        <v>6.9689896247136</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969870440635892</v>
+        <v>6.969575891886575</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950420680992261</v>
+        <v>6.950037744183325</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.899202963985227</v>
+        <v>6.898991378024891</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862712263196384</v>
+        <v>6.862489532095277</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84824984179974</v>
+        <v>6.848059036830376</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823296443757293</v>
+        <v>6.823441638598453</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841778529428291</v>
+        <v>6.841968439275167</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855090270527516</v>
+        <v>6.855505372756341</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.88715165941742</v>
+        <v>6.887352812318284</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889796687001756</v>
+        <v>6.889936265510085</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.876837970901201</v>
+        <v>6.877078970102068</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872684118350582</v>
+        <v>6.872526874111771</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846461738372524</v>
+        <v>6.846368387038607</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842704854798233</v>
+        <v>6.842549016585711</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.806562016045238</v>
+        <v>6.806788732260069</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.824004001730831</v>
+        <v>6.823994823114447</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819561959566317</v>
+        <v>6.819406378619991</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814316723371233</v>
+        <v>6.81413834968936</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808434544945268</v>
+        <v>6.808226802846816</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.804136654901373</v>
+        <v>6.803907445697928</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802521492519871</v>
+        <v>6.802270873399715</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783985802968866</v>
+        <v>6.783894236175051</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784877115790943</v>
+        <v>6.784710545182693</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775840849357794</v>
+        <v>6.775768401061361</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772330415691307</v>
+        <v>6.772099354952333</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768382870334678</v>
+        <v>6.768001966009582</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762428703204577</v>
+        <v>6.762782106552697</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753214966379685</v>
+        <v>6.755237434874852</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741230368641877</v>
+        <v>6.743299590677173</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.72917888040987</v>
+        <v>6.732515156760949</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.719013635993196</v>
+        <v>6.72625797512964</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712778545717618</v>
+        <v>6.722102808684228</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709182997529084</v>
+        <v>6.720616865071964</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.70797929700761</v>
+        <v>6.719997544997064</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.700241104563402</v>
+        <v>6.710912202413024</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.691544936615851</v>
+        <v>6.698700197834408</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.683225542285156</v>
+        <v>6.688177039430807</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.672747416287004</v>
+        <v>6.675160249077916</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.675498793209854</v>
+        <v>6.678384472095932</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.682903662721417</v>
+        <v>6.686889140863459</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.69993902912862</v>
+        <v>6.693985947902024</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.708788851211697</v>
+        <v>6.700944141413191</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.72108962751401</v>
+        <v>6.707503048793636</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.729350573281787</v>
+        <v>6.705819908136498</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.730844212719182</v>
+        <v>6.717116184772921</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.739902441993647</v>
+        <v>6.728503346826892</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.763966840103109</v>
+        <v>6.780283329623531</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.800368035713142</v>
+        <v>6.820362101364879</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.828540139863575</v>
+        <v>6.850108018971719</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>6.795272014863576</v>
+        <v>6.824588622090031</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -399,114 +399,962 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3">
-        <v>46304</v>
+        <v>44743</v>
       </c>
       <c r="B2">
-        <v>6.694155</v>
+        <v>6.69499090909091</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3">
-        <v>46311</v>
+        <v>44778</v>
       </c>
       <c r="B3">
-        <v>6.697129312975282</v>
+        <v>6.673973753517566</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3">
-        <v>46318</v>
+        <v>44806</v>
       </c>
       <c r="B4">
-        <v>6.704981877838739</v>
+        <v>6.679142866675689</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3">
-        <v>46325</v>
+        <v>44834</v>
       </c>
       <c r="B5">
-        <v>6.724186371311673</v>
+        <v>6.837424241545726</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3">
-        <v>46332</v>
+        <v>44869</v>
       </c>
       <c r="B6">
-        <v>6.743418562284115</v>
+        <v>6.812337676140215</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3">
-        <v>46339</v>
+        <v>44897</v>
       </c>
       <c r="B7">
-        <v>6.763702945885731</v>
+        <v>6.794531458612912</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3">
-        <v>46346</v>
+        <v>44932</v>
       </c>
       <c r="B8">
-        <v>6.781333778848653</v>
+        <v>6.850439179217833</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3">
-        <v>46353</v>
+        <v>44960</v>
       </c>
       <c r="B9">
-        <v>6.795280645859192</v>
+        <v>6.935440018341161</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3">
-        <v>46360</v>
+        <v>44988</v>
       </c>
       <c r="B10">
-        <v>6.806929849160435</v>
+        <v>6.917308094435005</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3">
-        <v>46367</v>
+        <v>45016</v>
       </c>
       <c r="B11">
-        <v>6.842723567415494</v>
+        <v>6.912375430337652</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3">
-        <v>46374</v>
+        <v>45051</v>
       </c>
       <c r="B12">
-        <v>6.857464562791332</v>
+        <v>6.910786268536967</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3">
-        <v>46381</v>
+        <v>45079</v>
       </c>
       <c r="B13">
-        <v>6.87177003556542</v>
+        <v>6.932890271839662</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3">
-        <v>46388</v>
+        <v>45107</v>
       </c>
       <c r="B14">
-        <v>6.881302883620275</v>
+        <v>7.008964210880152</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3">
+        <v>45142</v>
+      </c>
+      <c r="B15">
+        <v>7.025250654080553</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3">
+        <v>45170</v>
+      </c>
+      <c r="B16">
+        <v>7.040674608291788</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3">
+        <v>45205</v>
+      </c>
+      <c r="B17">
+        <v>7.128017077960847</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3">
+        <v>45233</v>
+      </c>
+      <c r="B18">
+        <v>7.215568924394407</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3">
+        <v>45261</v>
+      </c>
+      <c r="B19">
+        <v>7.213090138584138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3">
+        <v>45296</v>
+      </c>
+      <c r="B20">
+        <v>7.190698224409957</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3">
+        <v>45324</v>
+      </c>
+      <c r="B21">
+        <v>7.182037304684686</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3">
+        <v>45352</v>
+      </c>
+      <c r="B22">
+        <v>7.188721158173319</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3">
+        <v>45387</v>
+      </c>
+      <c r="B23">
+        <v>7.192419213014336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3">
+        <v>45415</v>
+      </c>
+      <c r="B24">
+        <v>7.157058663446328</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3">
+        <v>45443</v>
+      </c>
+      <c r="B25">
+        <v>7.182316132281979</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3">
+        <v>45478</v>
+      </c>
+      <c r="B26">
+        <v>7.217812548325404</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="3">
+        <v>45506</v>
+      </c>
+      <c r="B27">
+        <v>7.263988369441922</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="3">
+        <v>45541</v>
+      </c>
+      <c r="B28">
+        <v>7.271510077041134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="3">
+        <v>45569</v>
+      </c>
+      <c r="B29">
+        <v>7.144400288312168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="3">
+        <v>45597</v>
+      </c>
+      <c r="B30">
+        <v>7.115099906921387</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="3">
+        <v>45632</v>
+      </c>
+      <c r="B31">
+        <v>7.240300178527832</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="3">
+        <v>45660</v>
+      </c>
+      <c r="B32">
+        <v>7.295400142669678</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3">
+        <v>45688</v>
+      </c>
+      <c r="B33">
+        <v>7.243552224699795</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3">
+        <v>45716</v>
+      </c>
+      <c r="B34">
+        <v>7.250199794769287</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3">
+        <v>45751</v>
+      </c>
+      <c r="B35">
+        <v>7.26625379508566</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3">
+        <v>45779</v>
+      </c>
+      <c r="B36">
+        <v>7.2329</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3">
+        <v>45814</v>
+      </c>
+      <c r="B37">
+        <v>7.1737</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3">
+        <v>45821</v>
+      </c>
+      <c r="B38">
+        <v>7.070586310395566</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3">
+        <v>45828</v>
+      </c>
+      <c r="B39">
+        <v>7.086343362286877</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3">
+        <v>45835</v>
+      </c>
+      <c r="B40">
+        <v>7.10346949039587</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3">
+        <v>45842</v>
+      </c>
+      <c r="B41">
+        <v>7.112625667237227</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3">
+        <v>45849</v>
+      </c>
+      <c r="B42">
+        <v>7.141389252192583</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3">
+        <v>45856</v>
+      </c>
+      <c r="B43">
+        <v>7.151470646312874</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3">
+        <v>45863</v>
+      </c>
+      <c r="B44">
+        <v>7.154985606419348</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3">
+        <v>45870</v>
+      </c>
+      <c r="B45">
+        <v>7.168328480150986</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3">
+        <v>45877</v>
+      </c>
+      <c r="B46">
+        <v>7.183300144184605</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3">
+        <v>45884</v>
+      </c>
+      <c r="B47">
+        <v>7.19526151539864</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3">
+        <v>45891</v>
+      </c>
+      <c r="B48">
+        <v>7.197560973409812</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3">
+        <v>45898</v>
+      </c>
+      <c r="B49">
+        <v>7.192118401514888</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3">
+        <v>45905</v>
+      </c>
+      <c r="B50">
+        <v>7.175552095159594</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3">
+        <v>45912</v>
+      </c>
+      <c r="B51">
+        <v>7.180489591646186</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3">
+        <v>45919</v>
+      </c>
+      <c r="B52">
+        <v>7.184517792219868</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3">
+        <v>45926</v>
+      </c>
+      <c r="B53">
+        <v>7.189616104232949</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3">
+        <v>45933</v>
+      </c>
+      <c r="B54">
+        <v>7.18351659939459</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3">
+        <v>45940</v>
+      </c>
+      <c r="B55">
+        <v>7.182723219948238</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B56">
+        <v>7.183749168267408</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3">
+        <v>45954</v>
+      </c>
+      <c r="B57">
+        <v>7.169006068841391</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B58">
+        <v>7.155717237055971</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B59">
+        <v>7.148579210230821</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B60">
+        <v>7.144499826141448</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B61">
+        <v>7.124475000886253</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>45989</v>
+      </c>
+      <c r="B62">
+        <v>7.112013687712166</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3">
+        <v>45996</v>
+      </c>
+      <c r="B63">
+        <v>7.103502823233319</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3">
+        <v>46003</v>
+      </c>
+      <c r="B64">
+        <v>7.075836198960429</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3">
+        <v>46010</v>
+      </c>
+      <c r="B65">
+        <v>7.051253020587251</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3">
+        <v>46017</v>
+      </c>
+      <c r="B66">
+        <v>7.049644210936082</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3">
+        <v>46024</v>
+      </c>
+      <c r="B67">
+        <v>7.048331150095541</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3">
+        <v>46031</v>
+      </c>
+      <c r="B68">
+        <v>7.055466426058564</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3">
+        <v>46038</v>
+      </c>
+      <c r="B69">
+        <v>7.061423105210627</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B70">
+        <v>7.016770933242105</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B71">
+        <v>6.969021953420341</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46059</v>
+      </c>
+      <c r="B72">
+        <v>6.969607645754055</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B73">
+        <v>6.950078939879734</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46073</v>
+      </c>
+      <c r="B74">
+        <v>6.899014120836192</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B75">
+        <v>6.862513463892611</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B76">
+        <v>6.848079493747436</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B77">
+        <v>6.823425929067601</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B78">
+        <v>6.841947911338988</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B79">
+        <v>6.855460642032906</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B80">
+        <v>6.8873311393295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B81">
+        <v>6.889921264311523</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B82">
+        <v>6.877053067605814</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B83">
+        <v>6.872543813375225</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B84">
+        <v>6.846378421715967</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B85">
+        <v>6.842565771513414</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B86">
+        <v>6.8067643805761</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B87">
+        <v>6.823995860519325</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B88">
+        <v>6.819423197485482</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B89">
+        <v>6.814157628631494</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B90">
+        <v>6.808249233476311</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B91">
+        <v>6.803932163926324</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B92">
+        <v>6.802297854593855</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B93">
+        <v>6.783904112320983</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B94">
+        <v>6.784728453870221</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B95">
+        <v>6.775776150007211</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B96">
+        <v>6.772101529730718</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B97">
+        <v>6.768004807978651</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B98">
+        <v>6.762787677713723</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B99">
+        <v>6.755244967957032</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B100">
+        <v>6.743311739753903</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>6.732532958596934</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>6.726277240700259</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>6.722125655086327</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>6.720654215467624</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>6.720056662293722</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>6.710963433033265</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>6.698742184237439</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>6.688284256189159</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>6.675547428267042</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>6.678817765710709</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>6.687654673322786</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>6.695060409776946</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>6.702343348454233</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>6.709230595406472</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>6.708173168851666</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>6.719633731060807</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>6.732288727997643</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>6.782059757508635</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>6.819605370379112</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
         <v>46395</v>
       </c>
-      <c r="B15">
-        <v>6.883175273196826</v>
+      <c r="B120">
+        <v>6.845237472641688</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>6.82197303930503</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141389252192583</v>
+        <v>7.141386873709857</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151470646312874</v>
+        <v>7.151466666948888</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.154985606419348</v>
+        <v>7.154981681211705</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168328480150986</v>
+        <v>7.16832407717128</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183300144184605</v>
+        <v>7.183295971886376</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19526151539864</v>
+        <v>7.195257632863962</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197560973409812</v>
+        <v>7.197557462915725</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192118401514888</v>
+        <v>7.192115294632737</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175552095159594</v>
+        <v>7.175553842671285</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180489591646186</v>
+        <v>7.180493960382725</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184517792219868</v>
+        <v>7.184521892836705</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189616104232949</v>
+        <v>7.189620156801457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18351659939459</v>
+        <v>7.183523917931441</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182723219948238</v>
+        <v>7.182731773196659</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183749168267408</v>
+        <v>7.183756319936951</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.169006068841391</v>
+        <v>7.169012273451106</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155717237055971</v>
+        <v>7.155726469325013</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148579210230821</v>
+        <v>7.14858976236218</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144499826141448</v>
+        <v>7.144513012166097</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124475000886253</v>
+        <v>7.124485760355033</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.112013687712166</v>
+        <v>7.112028348180374</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103502823233319</v>
+        <v>7.103519490323298</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075836198960429</v>
+        <v>7.075854978426201</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.051253020587251</v>
+        <v>7.051272286286074</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049644210936082</v>
+        <v>7.04966459691918</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.048331150095541</v>
+        <v>7.048356295958319</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.055466426058564</v>
+        <v>7.055497257171301</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.061423105210627</v>
+        <v>7.06146569818941</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.016770933242105</v>
+        <v>7.01680972881063</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.969021953420341</v>
+        <v>6.969053721034525</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.969607645754055</v>
+        <v>6.969638853666767</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.950078939879734</v>
+        <v>6.950119447704446</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.899014120836192</v>
+        <v>6.89903648843908</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.862513463892611</v>
+        <v>6.862537002985516</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.848079493747436</v>
+        <v>6.848099625508073</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823425929067601</v>
+        <v>6.82341050302241</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.841947911338988</v>
+        <v>6.841927749235729</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.855460642032906</v>
+        <v>6.855416675850862</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.8873311393295</v>
+        <v>6.887309836088953</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.889921264311523</v>
+        <v>6.8899065101774</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877053067605814</v>
+        <v>6.87702759200941</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872543813375225</v>
+        <v>6.872560464299283</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846378421715967</v>
+        <v>6.846388290686294</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842565771513414</v>
+        <v>6.842582248970185</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.8067643805761</v>
+        <v>6.806740426521041</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823995860519325</v>
+        <v>6.823996868808223</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.819423197485482</v>
+        <v>6.81943971622914</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.814157628631494</v>
+        <v>6.814176564477636</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.808249233476311</v>
+        <v>6.808271270208699</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803932163926324</v>
+        <v>6.803956455206582</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.802297854593855</v>
+        <v>6.802324380558307</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783904112320983</v>
+        <v>6.783913817552432</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784728453870221</v>
+        <v>6.784746066069277</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775776150007211</v>
+        <v>6.775783780161812</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772101529730718</v>
+        <v>6.772103679559535</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768004807978651</v>
+        <v>6.768007599597589</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762787677713723</v>
+        <v>6.762793134348344</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.755244967957032</v>
+        <v>6.755252345474821</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743311739753903</v>
+        <v>6.743323650305701</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.732532958596934</v>
+        <v>6.732550447105057</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.726277240700259</v>
+        <v>6.726296185525601</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.722125655086327</v>
+        <v>6.722148124982263</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.720654215467624</v>
+        <v>6.720690967372576</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.720056662293722</v>
+        <v>6.720114933312592</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.710963433033265</v>
+        <v>6.711013978733595</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.698742184237439</v>
+        <v>6.698783678035601</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.688284256189159</v>
+        <v>6.688209113575045</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.675547428267042</v>
+        <v>6.675682362839071</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.678817765710709</v>
+        <v>6.678930268186794</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.687654673322786</v>
+        <v>6.687882297635753</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.695060409776946</v>
+        <v>6.695508008660681</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.702343348454233</v>
+        <v>6.703047452046521</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.709230595406472</v>
+        <v>6.710182839961748</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.708173168851666</v>
+        <v>6.709647888937365</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>6.719633731060807</v>
+        <v>6.721166025744903</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>6.732288727997643</v>
+        <v>6.73474529100541</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>6.782059757508635</v>
+        <v>6.782425922954253</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>6.819605370379112</v>
+        <v>6.817333754902148</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.845237472641688</v>
+        <v>6.839002238724439</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>6.82197303930503</v>
+        <v>6.815427170075177</v>
       </c>
     </row>
   </sheetData>
